--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52261-2022</t>
+          <t>A 5233-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44873</v>
+        <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,124 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52261-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44873</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
@@ -1709,144 +1821,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 5233-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5567-2023</t>
+          <t>A 64189-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44960</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 5567-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44960</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>Sårläka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 8939-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44979</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>2.7</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44917</v>
+        <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3422,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45279</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,14 +3490,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3531,42 +3536,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45118</v>
+        <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,13 +3606,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>12.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3634,49 +3639,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45119</v>
+        <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3705,16 +3710,11 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>12.4</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45558</v>
+        <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3815,18 +3815,23 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>13.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3840,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3856,42 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3901,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45119</v>
+        <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3926,7 +3931,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3938,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3950,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3966,39 +3971,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
@@ -4022,7 +4023,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4115,7 +4116,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,10 +4130,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45098</v>
+        <v>45558</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4145,10 +4146,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -4185,42 +4186,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4234,10 +4235,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,17 +4250,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4274,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4290,42 +4296,46 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4335,14 +4345,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44979</v>
+        <v>44917</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,13 +4364,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.7</v>
+        <v>15.8</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4372,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4384,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4396,46 +4401,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45119</v>
+        <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4464,13 +4469,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>13.1</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4510,35 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44455</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>44854</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44809</v>
+        <v>45610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45419</v>
+        <v>45747</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45469</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44979</v>
+        <v>45457</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5363,14 +5363,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44957</v>
+        <v>45344</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44979</v>
+        <v>44942</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5455,13 +5455,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5504,7 +5499,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5518,10 +5513,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44602</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5534,7 +5529,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5577,7 +5572,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5591,10 +5586,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45825</v>
+        <v>44574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5608,11 +5603,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5655,7 +5650,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>44809</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5685,7 +5680,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5728,7 +5723,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5742,10 +5737,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44574</v>
+        <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5759,11 +5754,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5806,7 +5801,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5820,10 +5815,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>45469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5836,7 +5831,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5874,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5888,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45737</v>
+        <v>46052</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5908,8 +5903,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45400</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45869</v>
+        <v>45737</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45869</v>
+        <v>44979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6127,8 +6127,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>8.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6176,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6190,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45086</v>
+        <v>45928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6244,7 +6249,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6258,10 +6263,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45139</v>
+        <v>45935</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6274,7 +6279,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6317,7 +6322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45610</v>
+        <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6347,7 +6352,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6390,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6404,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44509</v>
+        <v>45869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6419,13 +6424,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6485,7 +6485,7 @@
         <v>45610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6541,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45928</v>
+        <v>44509</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6570,8 +6570,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6614,7 +6619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6628,10 +6633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45457</v>
+        <v>45266</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6644,7 +6649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6687,7 +6692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6701,10 +6706,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45610</v>
+        <v>45196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6717,7 +6722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6760,7 +6765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6770,14 +6775,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45935</v>
+        <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6790,7 +6795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6833,7 +6838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45196</v>
+        <v>45974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6863,7 +6868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6906,7 +6911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6916,14 +6921,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45952</v>
+        <v>45974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6936,7 +6941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6979,7 +6984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6993,10 +6998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45113</v>
+        <v>45762</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7009,7 +7014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.2</v>
+        <v>11</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7052,7 +7057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7062,14 +7067,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45974</v>
+        <v>44908</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7082,7 +7087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7125,7 +7130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7139,10 +7144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45974</v>
+        <v>45149</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7155,7 +7160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7198,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7212,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45762</v>
+        <v>45400</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7228,7 +7233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7271,7 +7276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7281,14 +7286,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44908</v>
+        <v>44602</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7301,7 +7306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7344,7 +7349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7358,10 +7363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45140</v>
+        <v>45419</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7374,7 +7379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7417,7 +7422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44979</v>
+        <v>45280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7446,13 +7451,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7495,7 +7495,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7509,10 +7509,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45196</v>
+        <v>45173</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44942</v>
+        <v>45173</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7641,7 +7641,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46052</v>
+        <v>46170</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7670,13 +7670,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7719,7 +7714,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45469</v>
+        <v>46245</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7749,7 +7744,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7792,7 +7787,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7806,10 +7801,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45419</v>
+        <v>46245</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7822,7 +7817,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7865,7 +7860,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7879,10 +7874,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45062</v>
+        <v>46245</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7895,7 +7890,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7938,7 +7933,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7952,10 +7947,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45149</v>
+        <v>46244</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7968,7 +7963,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8011,7 +8006,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8021,14 +8016,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45209</v>
+        <v>46085</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8040,13 +8035,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8089,7 +8079,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8103,10 +8093,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45173</v>
+        <v>46210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8119,7 +8109,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>12.3</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8162,7 +8152,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8176,10 +8166,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46170</v>
+        <v>44941</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8192,7 +8182,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8235,7 +8225,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8249,10 +8239,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44735</v>
+        <v>45062</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8265,7 +8255,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8308,7 +8298,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8322,10 +8312,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45274</v>
+        <v>44979</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8337,8 +8327,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8381,7 +8376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8395,10 +8390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45280</v>
+        <v>45086</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8411,7 +8406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8454,7 +8449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8468,10 +8463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45239</v>
+        <v>45274</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8483,13 +8478,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8532,7 +8522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8546,10 +8536,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45266</v>
+        <v>46237</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8562,7 +8552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8605,7 +8595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8615,14 +8605,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45344</v>
+        <v>46237</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8635,7 +8625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8678,7 +8668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8692,10 +8682,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45173</v>
+        <v>44789</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8708,7 +8698,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8751,7 +8741,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8765,10 +8755,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45272</v>
+        <v>44957</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8781,7 +8771,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8824,7 +8814,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8838,10 +8828,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46237</v>
+        <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8854,7 +8844,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8897,7 +8887,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8911,10 +8901,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46237</v>
+        <v>45239</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8926,8 +8916,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8970,7 +8965,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8984,10 +8979,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46244</v>
+        <v>45469</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +8995,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9043,7 +9038,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9057,10 +9052,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46245</v>
+        <v>45610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9068,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9116,7 +9111,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9130,10 +9125,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44680</v>
+        <v>45139</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9146,7 +9141,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9189,7 +9184,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9203,10 +9198,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45189</v>
+        <v>45140</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9219,7 +9214,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9262,7 +9257,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9276,10 +9271,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46245</v>
+        <v>45184</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9292,7 +9287,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9335,7 +9330,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9349,10 +9344,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46245</v>
+        <v>45113</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9365,7 +9360,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9408,7 +9403,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9418,14 +9413,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45280</v>
+        <v>45561</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9438,7 +9433,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9481,7 +9476,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9491,14 +9486,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46085</v>
+        <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9506,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9554,7 +9549,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9568,10 +9563,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45610</v>
+        <v>45196</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9584,7 +9579,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9627,7 +9622,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9641,10 +9636,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46210</v>
+        <v>45209</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9656,8 +9651,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9700,7 +9700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45184</v>
+        <v>45419</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9773,7 +9773,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45520</v>
+        <v>45028</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45146</v>
+        <v>44979</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44789</v>
+        <v>44986</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45028</v>
+        <v>44680</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44986</v>
+        <v>45520</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45664</v>
+        <v>45189</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>7.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44941</v>
+        <v>45664</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10284,7 +10284,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10294,14 +10294,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45561</v>
+        <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10357,7 +10357,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10371,10 +10371,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45747</v>
+        <v>45146</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10447,7 +10447,7 @@
         <v>44574</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45779</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45789</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>45482</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44787</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>46198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 31142-2023</t>
+          <t>A 60057-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45113</v>
+        <v>45257</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,22 +861,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -897,9 +897,126 @@
         <v>9</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Stare
+Björktrast
+Ladusvala
+Rödvingetrast
+Tibast
+Havsörn
+Trana
+Törnskata</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 60057-2023 artfynd.xlsx", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 60057-2023 karta.png", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 60057-2023 georefererad karta.tif", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 60057-2023 FSC-klagomål.docx", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 60057-2023 FSC-klagomål mail.docx", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 60057-2023 tillsynsbegäran.docx", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 60057-2023 tillsynsbegäran mail.docx", "A 60057-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 60057-2023 prioriterade fågelarter.docx", "A 60057-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 31142-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45113</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Ask
 Skogsalm
@@ -912,153 +1029,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31142-2023 artfynd.xlsx", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31142-2023 karta.png", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31142-2023 georefererad karta.tif", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31142-2023 FSC-klagomål.docx", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31142-2023 FSC-klagomål mail.docx", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31142-2023 tillsynsbegäran.docx", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31142-2023 tillsynsbegäran mail.docx", "A 31142-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 31142-2023 prioriterade fågelarter.docx", "A 31142-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 60057-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45257</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Stare
-Björktrast
-Ladusvala
-Rödvingetrast
-Tibast
-Havsörn
-Trana
-Törnskata</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 60057-2023 artfynd.xlsx", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 60057-2023 karta.png", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 60057-2023 georefererad karta.tif", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 60057-2023 FSC-klagomål.docx", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 60057-2023 FSC-klagomål mail.docx", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 60057-2023 tillsynsbegäran.docx", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 60057-2023 tillsynsbegäran mail.docx", "A 60057-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 60057-2023 prioriterade fågelarter.docx", "A 60057-2023")</f>
         <v/>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5233-2026</t>
+          <t>A 52261-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46049</v>
+        <v>44873</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,120 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Hasselticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 5233-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Spillkråka
@@ -1709,144 +1817,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52261-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44873</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Hasselticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9268-2023</t>
+          <t>A 62013-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44980</v>
+        <v>45266</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,16 +1991,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2027,259 +2027,259 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Törnskata
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 16309-2022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44670</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 9268-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44980</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blodticka
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9268-2023 artfynd.xlsx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9268-2023 karta.png", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9268-2023 georefererad karta.tif", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9268-2023 FSC-klagomål.docx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9268-2023 FSC-klagomål mail.docx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9268-2023 tillsynsbegäran.docx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9268-2023 tillsynsbegäran mail.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 62013-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45266</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Törnskata
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 16309-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44670</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
         <v/>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64189-2023</t>
+          <t>A 12033-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2408,14 +2408,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>46085</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
@@ -2464,892 +2464,892 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 5567-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44960</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>17</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>5</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>17</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 5567-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44960</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
         <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>44965</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,37 +3490,32 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3529,49 +3524,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45119</v>
+        <v>44917</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3600,16 +3595,11 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>12.4</v>
+        <v>15.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3642,46 +3632,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,10 +3685,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45279</v>
+        <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,14 +3700,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3739,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3800,10 +3795,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45119</v>
+        <v>45279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3815,22 +3810,17 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>13.1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3854,49 +3844,49 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3896,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44979</v>
+        <v>45118</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3931,19 +3921,19 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3955,58 +3945,58 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4016,14 +4006,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46167</v>
+        <v>44979</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,20 +4031,20 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -4065,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4077,46 +4067,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4130,10 +4120,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45558</v>
+        <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4145,18 +4135,23 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>13.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4170,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4186,42 +4181,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4238,7 +4233,7 @@
         <v>45119</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4256,10 +4251,10 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.4</v>
+        <v>12.4</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4296,46 +4291,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4349,10 +4340,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44917</v>
+        <v>45558</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4365,13 +4356,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>15.8</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4401,46 +4392,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4454,10 +4445,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,17 +4460,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4494,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4510,35 +4506,39 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE37">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44455</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48309-2022</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4997,10 +4997,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44854</v>
+        <v>45274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5012,13 +5012,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5056,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5070,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45610</v>
+        <v>44809</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5086,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5129,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 48309-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5143,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45747</v>
+        <v>44854</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5163,8 +5158,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>45280</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45457</v>
+        <v>45419</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5363,14 +5363,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45344</v>
+        <v>45610</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44942</v>
+        <v>45239</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5455,8 +5455,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5499,7 +5504,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5513,10 +5518,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44979</v>
+        <v>45469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5529,7 +5534,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5572,7 +5577,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5586,10 +5591,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44574</v>
+        <v>45266</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5601,13 +5606,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44809</v>
+        <v>44979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45825</v>
+        <v>45344</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5752,13 +5752,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5801,7 +5796,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5815,10 +5810,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45469</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5831,7 +5826,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5874,7 +5869,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5888,10 +5883,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46052</v>
+        <v>44957</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5903,13 +5898,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5942,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5956,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>44574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5981,8 +5971,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6020,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6034,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45737</v>
+        <v>44979</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,8 +6049,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44979</v>
+        <v>45173</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6127,13 +6127,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>8.1</v>
+        <v>6.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6176,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6190,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45928</v>
+        <v>45272</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6206,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6249,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6263,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45935</v>
+        <v>44602</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6279,7 +6274,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6322,7 +6317,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6336,10 +6331,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45869</v>
+        <v>45928</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6352,7 +6347,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6390,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6404,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45869</v>
+        <v>45935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6468,7 +6463,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45610</v>
+        <v>45762</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6493,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>11</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6551,14 +6546,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44509</v>
+        <v>44908</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6570,13 +6565,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6619,7 +6609,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6633,10 +6623,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45266</v>
+        <v>45400</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6649,7 +6639,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6692,7 +6682,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6702,14 +6692,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45196</v>
+        <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6722,7 +6712,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6765,7 +6755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6775,14 +6765,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45952</v>
+        <v>45086</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6795,7 +6785,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6838,7 +6828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6852,10 +6842,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45974</v>
+        <v>45139</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6868,7 +6858,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6911,7 +6901,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6925,10 +6915,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45974</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6941,7 +6931,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6984,7 +6974,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45762</v>
+        <v>44509</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7013,8 +7003,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7057,7 +7052,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7067,14 +7062,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44908</v>
+        <v>45974</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7087,7 +7082,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7130,7 +7125,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7144,10 +7139,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45149</v>
+        <v>45974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7160,7 +7155,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7203,7 +7198,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7217,10 +7212,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45400</v>
+        <v>45457</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7233,7 +7228,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7276,7 +7271,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7290,10 +7285,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44602</v>
+        <v>45610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7306,7 +7301,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7349,7 +7344,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7363,10 +7358,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45419</v>
+        <v>44680</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7379,7 +7374,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7422,7 +7417,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45280</v>
+        <v>45189</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7452,7 +7447,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7495,7 +7490,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7509,10 +7504,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45173</v>
+        <v>45280</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7525,7 +7520,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7568,7 +7563,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7582,10 +7577,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45173</v>
+        <v>45196</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7598,7 +7593,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>12.3</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7641,7 +7636,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7655,10 +7650,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46170</v>
+        <v>45113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7666,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7714,7 +7709,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7728,10 +7723,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46245</v>
+        <v>46170</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7739,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7787,7 +7782,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7801,10 +7796,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46245</v>
+        <v>45610</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7812,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7860,7 +7855,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7874,10 +7869,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46245</v>
+        <v>46052</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7889,8 +7884,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46244</v>
+        <v>45184</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>6.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8016,14 +8016,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46085</v>
+        <v>45140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8093,10 +8093,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46210</v>
+        <v>44979</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8108,8 +8108,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8152,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8166,10 +8171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44941</v>
+        <v>45196</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8225,7 +8230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8239,10 +8244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45062</v>
+        <v>44942</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8298,7 +8303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8312,10 +8317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44979</v>
+        <v>45520</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8327,13 +8332,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45086</v>
+        <v>46244</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8463,10 +8463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45274</v>
+        <v>46245</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46237</v>
+        <v>45469</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8595,7 +8595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8668,7 +8668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44789</v>
+        <v>46245</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8741,7 +8741,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8755,10 +8755,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44957</v>
+        <v>45419</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8814,7 +8814,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8824,14 +8824,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45272</v>
+        <v>46085</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8901,10 +8901,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45239</v>
+        <v>46210</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8916,13 +8916,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8965,7 +8960,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,10 +8974,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45469</v>
+        <v>45146</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +8990,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9038,7 +9033,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9052,10 +9047,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45610</v>
+        <v>45062</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9063,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9111,7 +9106,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9125,10 +9120,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45139</v>
+        <v>45149</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9136,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9184,7 +9179,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9198,10 +9193,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45140</v>
+        <v>45209</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9213,8 +9208,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45184</v>
+        <v>45173</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.8</v>
+        <v>12.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45113</v>
+        <v>44789</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9413,14 +9413,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45561</v>
+        <v>44735</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9476,7 +9476,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45280</v>
+        <v>45028</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9549,7 +9549,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45196</v>
+        <v>44986</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9622,7 +9622,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45209</v>
+        <v>45664</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9651,13 +9651,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9700,7 +9695,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9714,10 +9709,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45419</v>
+        <v>44941</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9725,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9773,7 +9768,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9783,14 +9778,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45028</v>
+        <v>45561</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9798,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9841,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9860,10 +9855,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44979</v>
+        <v>45747</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9871,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9914,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9928,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44986</v>
+        <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9948,8 +9943,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44680</v>
+        <v>45779</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45520</v>
+        <v>46237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45189</v>
+        <v>46237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45664</v>
+        <v>45789</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10240,8 +10240,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10284,7 +10289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10298,10 +10303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45610</v>
+        <v>45825</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10313,8 +10318,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10357,7 +10367,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10371,10 +10381,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45146</v>
+        <v>45610</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10387,7 +10397,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10430,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10444,10 +10454,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44574</v>
+        <v>45737</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10459,13 +10469,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10508,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10522,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45779</v>
+        <v>45869</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10538,7 +10543,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10581,7 +10586,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10595,10 +10600,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45789</v>
+        <v>45869</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10610,13 +10615,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I120" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10676,7 +10676,7 @@
         <v>45482</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>44787</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>46198</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE123"/>
+  <dimension ref="A1:AE122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 60057-2023</t>
+          <t>A 31142-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45257</v>
+        <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -861,22 +861,22 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>2</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -897,9 +897,126 @@
         <v>9</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Skogsalm
+Entita
+Jungfrulin
+Talltita
+Gröngöling
+Grönsiska
+Havsörn
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31142-2023 artfynd.xlsx", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31142-2023 karta.png", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31142-2023 georefererad karta.tif", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31142-2023 FSC-klagomål.docx", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31142-2023 FSC-klagomål mail.docx", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31142-2023 tillsynsbegäran.docx", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31142-2023 tillsynsbegäran mail.docx", "A 31142-2023")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 31142-2023 prioriterade fågelarter.docx", "A 31142-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 60057-2023</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45257</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Stare
@@ -912,153 +1029,36 @@
 Törnskata</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 60057-2023 artfynd.xlsx", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 60057-2023 karta.png", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 60057-2023 georefererad karta.tif", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 60057-2023 FSC-klagomål.docx", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 60057-2023 FSC-klagomål mail.docx", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 60057-2023 tillsynsbegäran.docx", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 60057-2023 tillsynsbegäran mail.docx", "A 60057-2023")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 60057-2023 prioriterade fågelarter.docx", "A 60057-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 31142-2023</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45113</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Skogsalm
-Entita
-Jungfrulin
-Talltita
-Gröngöling
-Grönsiska
-Havsörn
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31142-2023 artfynd.xlsx", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31142-2023 karta.png", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31142-2023 georefererad karta.tif", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31142-2023 FSC-klagomål.docx", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31142-2023 FSC-klagomål mail.docx", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31142-2023 tillsynsbegäran.docx", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31142-2023 tillsynsbegäran mail.docx", "A 31142-2023")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 31142-2023 prioriterade fågelarter.docx", "A 31142-2023")</f>
         <v/>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52261-2022</t>
+          <t>A 5233-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44873</v>
+        <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,124 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52261-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44873</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
@@ -1709,144 +1821,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 5233-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62013-2023</t>
+          <t>A 9268-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45266</v>
+        <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,17 +1991,17 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2027,259 +2027,259 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blodticka
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9268-2023 artfynd.xlsx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9268-2023 karta.png", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9268-2023 georefererad karta.tif", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9268-2023 FSC-klagomål.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9268-2023 FSC-klagomål mail.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9268-2023 tillsynsbegäran.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9268-2023 tillsynsbegäran mail.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62013-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Törnskata
 Gullviva</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 16309-2022</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>44670</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>7.7</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 9268-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blodticka
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9268-2023 artfynd.xlsx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9268-2023 karta.png", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9268-2023 georefererad karta.tif", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9268-2023 FSC-klagomål.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9268-2023 FSC-klagomål mail.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9268-2023 tillsynsbegäran.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9268-2023 tillsynsbegäran mail.docx", "A 9268-2023")</f>
         <v/>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12033-2026</t>
+          <t>A 64189-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2408,14 +2408,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46085</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
@@ -2464,892 +2464,892 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Fjällvråk
 Havsörn</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 5567-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>44960</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>10.1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Sårläka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="D25" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U25" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>17</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="D26" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>5</v>
-      </c>
-      <c r="U24" t="n">
-        <v>5</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
         <v/>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
         <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44965</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,17 +3490,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3515,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3524,49 +3529,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44917</v>
+        <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3595,11 +3600,16 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>15.8</v>
+        <v>12.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3632,46 +3642,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3685,10 +3695,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46167</v>
+        <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3700,19 +3710,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3739,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3795,10 +3800,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45279</v>
+        <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3810,18 +3815,23 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>13.1</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3835,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3844,49 +3854,49 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3896,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45118</v>
+        <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3921,20 +3931,20 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -3945,58 +3955,58 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4006,14 +4016,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44979</v>
+        <v>45558</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4025,25 +4035,20 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4055,10 +4060,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4071,42 +4076,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4123,7 +4128,7 @@
         <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4141,16 +4146,16 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4165,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4181,42 +4186,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4230,10 +4239,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45119</v>
+        <v>44917</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4245,16 +4254,11 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>12.4</v>
+        <v>15.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4287,46 +4291,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4340,10 +4344,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45558</v>
+        <v>46167</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4355,11 +4359,16 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -4392,46 +4401,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4445,10 +4454,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45119</v>
+        <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4460,23 +4469,18 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.4</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4490,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4506,39 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 49657-2021</t>
+          <t>A 48309-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44455</v>
+        <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4939,8 +4939,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>7.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4983,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4997,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45274</v>
+        <v>45747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5013,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5056,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5070,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44809</v>
+        <v>45610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5086,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5129,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 48309-2022</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5143,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44854</v>
+        <v>45457</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5158,13 +5163,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.4</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45280</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5290,14 +5290,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45419</v>
+        <v>45344</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45610</v>
+        <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45239</v>
+        <v>44809</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5455,13 +5455,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5504,7 +5499,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5518,10 +5513,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45469</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5534,7 +5529,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5577,7 +5572,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5591,10 +5586,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45266</v>
+        <v>44574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5606,8 +5601,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5664,10 +5664,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>45469</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45344</v>
+        <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5752,8 +5752,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5796,7 +5801,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5813,7 +5818,7 @@
         <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5825,8 +5830,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>8.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5869,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5883,10 +5893,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44957</v>
+        <v>45610</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5899,7 +5909,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5942,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5956,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44574</v>
+        <v>45737</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5971,13 +5981,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6020,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6034,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44979</v>
+        <v>45928</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6049,13 +6054,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>8.1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45173</v>
+        <v>45935</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45272</v>
+        <v>45869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44602</v>
+        <v>45869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45928</v>
+        <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6346,8 +6346,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6390,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6404,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45935</v>
+        <v>45266</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6420,7 +6425,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6463,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45762</v>
+        <v>45610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6493,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6536,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6546,14 +6551,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44908</v>
+        <v>45196</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6566,7 +6571,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6619,14 +6624,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45400</v>
+        <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6639,7 +6644,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6682,7 +6687,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6692,14 +6697,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45952</v>
+        <v>46052</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6711,8 +6716,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6755,7 +6765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6769,10 +6779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45086</v>
+        <v>45974</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6785,7 +6795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6828,7 +6838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6842,10 +6852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45139</v>
+        <v>45974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6858,7 +6868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6901,7 +6911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6915,10 +6925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45610</v>
+        <v>45149</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6931,7 +6941,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44509</v>
+        <v>45400</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7003,13 +7013,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7052,7 +7057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7066,10 +7071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45974</v>
+        <v>44602</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7082,7 +7087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7125,7 +7130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7139,10 +7144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45974</v>
+        <v>45419</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7155,7 +7160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7198,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7212,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45457</v>
+        <v>45280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7228,7 +7233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7271,7 +7276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7285,10 +7290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45610</v>
+        <v>45173</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7301,7 +7306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7344,7 +7349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7358,10 +7363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44680</v>
+        <v>45173</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7374,7 +7379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>12.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7417,7 +7422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45189</v>
+        <v>45762</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7452,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7490,7 +7495,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7500,14 +7505,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45280</v>
+        <v>44908</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7525,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7563,7 +7568,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7577,10 +7582,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45196</v>
+        <v>44941</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7598,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7636,7 +7641,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7650,10 +7655,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45113</v>
+        <v>45062</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7671,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7709,7 +7714,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7723,10 +7728,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46170</v>
+        <v>44979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7738,8 +7743,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7782,7 +7792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7796,10 +7806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45610</v>
+        <v>45086</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7812,7 +7822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7855,7 +7865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7869,10 +7879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46052</v>
+        <v>45274</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7884,13 +7894,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7933,7 +7938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7947,10 +7952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45184</v>
+        <v>44789</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8006,7 +8011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8020,10 +8025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45140</v>
+        <v>44957</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8041,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8079,7 +8084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8093,10 +8098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44979</v>
+        <v>45272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8108,13 +8113,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45196</v>
+        <v>45239</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8186,8 +8186,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>5.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8230,7 +8235,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8244,10 +8249,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44942</v>
+        <v>45469</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8265,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8308,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8317,10 +8322,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45520</v>
+        <v>45610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8338,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8381,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8390,10 +8395,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46244</v>
+        <v>45139</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8411,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8449,7 +8454,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8463,10 +8468,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46245</v>
+        <v>46170</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8484,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8522,7 +8527,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8536,10 +8541,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45469</v>
+        <v>45140</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8557,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8595,7 +8600,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8609,10 +8614,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46245</v>
+        <v>45184</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8630,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.8</v>
+        <v>6.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8668,7 +8673,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8682,10 +8687,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46245</v>
+        <v>45113</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8703,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8741,7 +8746,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8751,14 +8756,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45419</v>
+        <v>45561</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8771,7 +8776,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8814,7 +8819,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8824,14 +8829,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46085</v>
+        <v>45280</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8844,7 +8849,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8887,7 +8892,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8901,10 +8906,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46210</v>
+        <v>45196</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8917,7 +8922,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8960,7 +8965,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8974,10 +8979,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45146</v>
+        <v>46245</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8990,7 +8995,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9033,7 +9038,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9047,10 +9052,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45062</v>
+        <v>46245</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9063,7 +9068,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9106,7 +9111,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9120,10 +9125,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45149</v>
+        <v>46245</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9136,7 +9141,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9179,7 +9184,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9193,10 +9198,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45209</v>
+        <v>46244</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9208,13 +9213,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45173</v>
+        <v>45209</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9286,8 +9286,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9330,7 +9335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9340,14 +9345,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44789</v>
+        <v>46085</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9403,7 +9408,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9417,10 +9422,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44735</v>
+        <v>45419</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9438,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9476,7 +9481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9490,10 +9495,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45028</v>
+        <v>46210</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9549,7 +9554,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9563,10 +9568,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44986</v>
+        <v>45028</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9584,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9622,7 +9627,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9636,10 +9641,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45664</v>
+        <v>44979</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9652,7 +9657,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9695,7 +9700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9709,10 +9714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44941</v>
+        <v>44986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9725,7 +9730,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9768,7 +9773,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9778,14 +9783,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45561</v>
+        <v>44680</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9798,7 +9803,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9841,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9855,10 +9860,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45747</v>
+        <v>45520</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9871,7 +9876,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9914,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9928,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44574</v>
+        <v>45189</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9943,13 +9948,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45779</v>
+        <v>45664</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46237</v>
+        <v>45610</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46237</v>
+        <v>45146</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45789</v>
+        <v>44574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10289,7 +10289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10303,10 +10303,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45825</v>
+        <v>45779</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10318,13 +10318,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10367,7 +10362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10381,10 +10376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45610</v>
+        <v>46237</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10397,7 +10392,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.4</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10440,7 +10435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10454,10 +10449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45737</v>
+        <v>46237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45869</v>
+        <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10542,8 +10537,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10586,24 +10586,24 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>S 2697-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45869</v>
+        <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10659,7 +10659,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>S 2697-2024</t>
+          <t>S 4477-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10669,87 +10669,87 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>44787</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>S 1845-2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D121" s="1" t="n">
-        <v>45482</v>
-      </c>
-      <c r="E121" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I121" t="n">
-        <v>6</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>S 4477-2022</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Skogsbilväg</t>
-        </is>
-      </c>
       <c r="D122" s="1" t="n">
-        <v>44787</v>
+        <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10801,79 +10801,6 @@
         <v>0</v>
       </c>
       <c r="V122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>S 1845-2026</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>46198</v>
-      </c>
-      <c r="E123" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I123" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5233-2026</t>
+          <t>A 52261-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46049</v>
+        <v>44873</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,120 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Hasselticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 5233-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Spillkråka
@@ -1709,144 +1817,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52261-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44873</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Hasselticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64189-2023</t>
+          <t>A 5567-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Sårläka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="D24" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 10059-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>17</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 5567-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44960</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45098</v>
+        <v>44917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>15.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3422,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>45279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,19 +3490,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3536,42 +3531,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45119</v>
+        <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3606,13 +3601,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12.4</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3639,49 +3634,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45279</v>
+        <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,14 +3705,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,42 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44979</v>
+        <v>45558</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,25 +3925,20 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3955,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3971,42 +3966,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4020,10 +4015,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45558</v>
+        <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4035,14 +4030,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4076,42 +4076,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4125,10 +4129,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45119</v>
+        <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,19 +4144,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4186,46 +4185,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4239,10 +4234,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44917</v>
+        <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4255,17 +4250,17 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4279,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4291,46 +4286,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4340,14 +4335,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46167</v>
+        <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4365,20 +4360,20 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -4389,10 +4384,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4401,46 +4396,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,8 +4464,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>13.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4510,35 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45747</v>
+        <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45610</v>
+        <v>45419</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45457</v>
+        <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5290,14 +5290,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45344</v>
+        <v>44957</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44942</v>
+        <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5382,8 +5382,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>8.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5431,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5445,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44809</v>
+        <v>44602</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5456,7 +5461,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5516,7 +5521,7 @@
         <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5589,7 +5594,7 @@
         <v>44574</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5650,7 +5655,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45469</v>
+        <v>45825</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5679,8 +5684,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5723,7 +5733,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5737,10 +5747,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45825</v>
+        <v>45400</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5752,13 +5762,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5801,7 +5806,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5815,10 +5820,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5830,13 +5835,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45610</v>
+        <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45737</v>
+        <v>45086</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45928</v>
+        <v>45139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45935</v>
+        <v>45610</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45869</v>
+        <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6200,8 +6200,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6261,7 +6266,7 @@
         <v>45869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6317,7 +6322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44509</v>
+        <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6346,13 +6351,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45266</v>
+        <v>45457</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6468,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6485,7 +6485,7 @@
         <v>45610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45196</v>
+        <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6614,7 +6614,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6624,14 +6624,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45952</v>
+        <v>45762</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6687,7 +6687,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6701,10 +6701,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46052</v>
+        <v>45196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6716,13 +6716,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6765,7 +6760,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6775,14 +6770,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45974</v>
+        <v>44908</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6795,7 +6790,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6838,7 +6833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6852,10 +6847,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45974</v>
+        <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6868,7 +6863,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6911,7 +6906,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6925,10 +6920,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45149</v>
+        <v>45928</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6941,7 +6936,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6984,7 +6979,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6998,10 +6993,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45400</v>
+        <v>45935</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7057,7 +7052,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7071,10 +7066,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44602</v>
+        <v>45140</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7087,7 +7082,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7130,7 +7125,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7144,10 +7139,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45419</v>
+        <v>44979</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7159,8 +7154,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7203,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7217,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45280</v>
+        <v>45196</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45173</v>
+        <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7349,7 +7349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7363,10 +7363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45173</v>
+        <v>46170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>12.3</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7422,7 +7422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7436,10 +7436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45762</v>
+        <v>45469</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7495,7 +7495,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7505,14 +7505,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44908</v>
+        <v>45952</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44941</v>
+        <v>45419</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7641,7 +7641,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45062</v>
+        <v>45974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44979</v>
+        <v>45974</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7743,13 +7743,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7792,7 +7787,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7806,10 +7801,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45086</v>
+        <v>45062</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7822,7 +7817,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7865,7 +7860,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7879,10 +7874,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45274</v>
+        <v>46244</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7895,7 +7890,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7938,7 +7933,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7952,10 +7947,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44789</v>
+        <v>46245</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7968,7 +7963,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8011,7 +8006,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8025,10 +8020,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44957</v>
+        <v>46245</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8041,7 +8036,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8084,7 +8079,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8098,10 +8093,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45272</v>
+        <v>46245</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8109,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8152,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8171,10 +8166,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45239</v>
+        <v>45149</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8186,13 +8181,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8235,7 +8225,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8249,10 +8239,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45469</v>
+        <v>45209</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8264,8 +8254,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8308,7 +8303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8322,10 +8317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45610</v>
+        <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8338,7 +8333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8381,7 +8376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8395,10 +8390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45139</v>
+        <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8411,7 +8406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8454,7 +8449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8464,14 +8459,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46170</v>
+        <v>46085</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8484,7 +8479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8527,7 +8522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8541,10 +8536,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45140</v>
+        <v>45274</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8557,7 +8552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8600,7 +8595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8614,10 +8609,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45184</v>
+        <v>46210</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8630,7 +8625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.8</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8673,7 +8668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8687,10 +8682,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45113</v>
+        <v>45280</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8703,7 +8698,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8746,7 +8741,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8756,14 +8751,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45561</v>
+        <v>45239</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8775,8 +8770,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45280</v>
+        <v>45266</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8892,7 +8892,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8902,14 +8902,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45196</v>
+        <v>45344</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8965,7 +8965,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46245</v>
+        <v>45173</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46245</v>
+        <v>45272</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9111,7 +9111,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9125,10 +9125,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9198,10 +9198,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45209</v>
+        <v>44680</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9286,13 +9286,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9335,7 +9330,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9345,14 +9340,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46085</v>
+        <v>45189</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9365,7 +9360,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9408,7 +9403,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9422,10 +9417,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45419</v>
+        <v>45280</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9438,7 +9433,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>5.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9481,7 +9476,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9495,10 +9490,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46210</v>
+        <v>45610</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9506,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9554,7 +9549,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9568,10 +9563,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45028</v>
+        <v>45184</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9584,7 +9579,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9627,7 +9622,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9641,10 +9636,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44979</v>
+        <v>46052</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9656,8 +9651,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9700,7 +9700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9714,10 +9714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44986</v>
+        <v>45520</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9773,7 +9773,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44680</v>
+        <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45520</v>
+        <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45189</v>
+        <v>45028</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45664</v>
+        <v>44986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45610</v>
+        <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45146</v>
+        <v>44941</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10211,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10221,14 +10221,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44574</v>
+        <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10240,13 +10240,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10289,7 +10284,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10303,10 +10298,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45779</v>
+        <v>45747</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10319,7 +10314,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10362,7 +10357,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10376,10 +10371,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46237</v>
+        <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10391,8 +10386,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10435,7 +10435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46237</v>
+        <v>45779</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10525,7 +10525,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44873</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>46049</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5567-2023</t>
+          <t>A 64189-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44960</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 5567-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44960</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Sårläka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 12033-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>2.4</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Fjällvråk
 Havsörn</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AE19">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 8939-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44979</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>2.7</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44917</v>
+        <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3422,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45279</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,14 +3490,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3531,42 +3536,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45118</v>
+        <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,13 +3606,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>12.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3634,49 +3639,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46167</v>
+        <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3705,19 +3710,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,42 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45558</v>
+        <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,21 +3925,26 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -3950,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3966,42 +3971,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4015,10 +4020,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45119</v>
+        <v>45558</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4030,19 +4035,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4076,46 +4076,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,10 +4125,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45098</v>
+        <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,14 +4140,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4185,42 +4186,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4234,10 +4239,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44965</v>
+        <v>46167</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,17 +4254,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4274,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4286,46 +4296,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4335,14 +4345,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44979</v>
+        <v>44917</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,13 +4364,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.7</v>
+        <v>15.8</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4372,7 +4377,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4384,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4396,46 +4401,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45119</v>
+        <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4464,13 +4469,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>13.1</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4510,35 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44809</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45419</v>
+        <v>45747</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45469</v>
+        <v>45457</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44979</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5290,14 +5290,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44957</v>
+        <v>45344</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44979</v>
+        <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5382,13 +5382,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5431,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44602</v>
+        <v>44809</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5461,7 +5456,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5504,7 +5499,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5518,10 +5513,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44979</v>
+        <v>45469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5534,7 +5529,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5577,7 +5572,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5591,10 +5586,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44574</v>
+        <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5612,7 +5607,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>8.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5655,7 +5650,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45825</v>
+        <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5686,11 +5681,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5733,7 +5728,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5747,10 +5742,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45400</v>
+        <v>45266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5763,7 +5758,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5806,7 +5801,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5820,10 +5815,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>45196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5836,7 +5831,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5874,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5888,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45737</v>
+        <v>44574</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5908,8 +5903,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45086</v>
+        <v>45762</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45139</v>
+        <v>44908</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45610</v>
+        <v>45149</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44509</v>
+        <v>45400</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6200,13 +6200,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6249,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6263,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45869</v>
+        <v>44979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6279,7 +6274,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6322,7 +6317,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6336,10 +6331,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45869</v>
+        <v>44602</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6352,7 +6347,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6390,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6404,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45457</v>
+        <v>45419</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6425,7 +6420,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6468,7 +6463,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6482,10 +6477,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45610</v>
+        <v>45280</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6493,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6555,10 +6550,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45610</v>
+        <v>45928</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6571,7 +6566,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45762</v>
+        <v>45935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6644,7 +6639,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6687,7 +6682,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6701,10 +6696,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45196</v>
+        <v>45173</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6717,7 +6712,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6760,7 +6755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6770,14 +6765,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44908</v>
+        <v>45173</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6790,7 +6785,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>12.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6833,7 +6828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6843,14 +6838,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45113</v>
+        <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6863,7 +6858,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6906,7 +6901,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6920,10 +6915,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45928</v>
+        <v>45974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6936,7 +6931,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6979,7 +6974,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6993,10 +6988,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45935</v>
+        <v>45974</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7009,7 +7004,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7052,7 +7047,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7066,10 +7061,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45140</v>
+        <v>44941</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7082,7 +7077,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7125,7 +7120,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7139,10 +7134,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44979</v>
+        <v>45062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7154,13 +7149,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45196</v>
+        <v>44979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7232,8 +7222,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7276,7 +7271,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7290,10 +7285,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44942</v>
+        <v>45086</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7306,7 +7301,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7349,7 +7344,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7363,10 +7358,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46170</v>
+        <v>45274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7379,7 +7374,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7422,7 +7417,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45469</v>
+        <v>44789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7452,7 +7447,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7495,7 +7490,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7505,14 +7500,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45952</v>
+        <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7525,7 +7520,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7568,7 +7563,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7582,10 +7577,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45419</v>
+        <v>45272</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7598,7 +7593,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7641,7 +7636,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7655,10 +7650,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45974</v>
+        <v>46170</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7666,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7714,7 +7709,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7728,10 +7723,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45974</v>
+        <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7743,8 +7738,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45062</v>
+        <v>45469</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7860,7 +7860,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46244</v>
+        <v>45610</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46245</v>
+        <v>45139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8006,7 +8006,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8020,10 +8020,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46245</v>
+        <v>46052</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8035,8 +8035,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8079,7 +8084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8093,10 +8098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46245</v>
+        <v>45140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8152,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8166,10 +8171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45149</v>
+        <v>45184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8225,7 +8230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8239,10 +8244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45209</v>
+        <v>45113</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8254,13 +8259,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45173</v>
+        <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>12.3</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44735</v>
+        <v>45280</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8459,14 +8459,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46085</v>
+        <v>45196</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45274</v>
+        <v>46245</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8595,7 +8595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8668,7 +8668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45280</v>
+        <v>45209</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8697,8 +8697,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8741,7 +8746,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8755,10 +8760,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45239</v>
+        <v>46245</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8770,13 +8775,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45266</v>
+        <v>46244</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8892,7 +8892,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8902,14 +8902,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45344</v>
+        <v>45419</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8965,7 +8965,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45173</v>
+        <v>45028</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45272</v>
+        <v>44979</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9111,7 +9111,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9121,14 +9121,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46237</v>
+        <v>46085</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9198,10 +9198,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46237</v>
+        <v>44986</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9274,7 +9274,7 @@
         <v>44680</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45189</v>
+        <v>46210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.6</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45280</v>
+        <v>45520</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9476,7 +9476,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45610</v>
+        <v>45189</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9549,7 +9549,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45184</v>
+        <v>45664</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.8</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9622,7 +9622,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9636,10 +9636,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46052</v>
+        <v>45610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9651,13 +9651,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9700,7 +9695,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9714,10 +9709,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45520</v>
+        <v>45146</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9725,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9773,7 +9768,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9787,10 +9782,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45146</v>
+        <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9802,8 +9797,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44789</v>
+        <v>45779</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45028</v>
+        <v>45789</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9948,8 +9948,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44986</v>
+        <v>46237</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10027,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45664</v>
+        <v>46237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10100,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44941</v>
+        <v>45825</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10167,8 +10172,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10211,7 +10221,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10221,14 +10231,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45561</v>
+        <v>45610</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10251,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10284,7 +10294,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10298,10 +10308,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45747</v>
+        <v>45737</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10324,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10357,7 +10367,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10371,10 +10381,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44574</v>
+        <v>45869</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10386,13 +10396,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10435,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10449,10 +10454,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45779</v>
+        <v>45869</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10465,7 +10470,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10508,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10522,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45789</v>
+        <v>45610</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10537,13 +10542,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>44873</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>46049</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44937</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45131</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>46085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>45558</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46167</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>44917</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45747</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>45457</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45344</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44809</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>45469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>45266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>45196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44574</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45762</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44908</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45149</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45400</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>44602</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>45419</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>45280</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45928</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>45935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>45173</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>45173</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>45974</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>44941</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
         <v>45062</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>44979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>45086</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>45274</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>45272</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         <v>46170</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>45239</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>45469</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>45610</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45139</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>46052</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45140</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45184</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>45113</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>45280</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>45196</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>46245</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>46245</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>45209</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>46245</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>46244</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>45419</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45028</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9055,7 +9055,7 @@
         <v>44979</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>46085</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9201,7 +9201,7 @@
         <v>44986</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>44680</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>46210</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45520</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45189</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45664</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45146</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44574</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45779</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45789</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>46237</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>46237</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45825</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>45610</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>45737</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         <v>45869</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>45869</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>45610</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52261-2022</t>
+          <t>A 5233-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44873</v>
+        <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,124 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52261-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44873</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
@@ -1709,144 +1821,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 5233-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44937</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>44621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>45131</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>46085</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45196</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44979</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45558</v>
+        <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4035,11 +4035,16 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -4072,46 +4077,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4125,10 +4130,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45119</v>
+        <v>45558</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,19 +4145,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4186,46 +4186,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4239,10 +4235,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46167</v>
+        <v>45119</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4260,13 +4256,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.9</v>
+        <v>5.4</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4296,39 +4292,43 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
         <v>44917</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>45747</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45747</v>
+        <v>45610</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5151,7 +5151,7 @@
         <v>45457</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>45344</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44809</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>45469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>45266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5801,7 +5801,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45196</v>
+        <v>44574</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5830,8 +5830,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5874,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5888,10 +5893,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44574</v>
+        <v>45196</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5903,13 +5908,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45762</v>
+        <v>45610</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6035,14 +6035,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44908</v>
+        <v>45762</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6108,14 +6108,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45149</v>
+        <v>44908</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45400</v>
+        <v>44979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44979</v>
+        <v>45149</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6317,7 +6317,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44602</v>
+        <v>45400</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6390,7 +6390,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6404,10 +6404,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45419</v>
+        <v>45928</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6477,10 +6477,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45280</v>
+        <v>45935</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6536,7 +6536,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6550,10 +6550,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45928</v>
+        <v>44602</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6609,7 +6609,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6619,14 +6619,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45935</v>
+        <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45173</v>
+        <v>45419</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.2</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6755,7 +6755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6769,10 +6769,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45173</v>
+        <v>45280</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>12.3</v>
+        <v>5.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6838,14 +6838,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45952</v>
+        <v>45974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6918,7 +6918,7 @@
         <v>45974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45974</v>
+        <v>45173</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7047,7 +7047,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44941</v>
+        <v>45173</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>12.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7120,7 +7120,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7134,10 +7134,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45062</v>
+        <v>46170</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44979</v>
+        <v>44941</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7222,13 +7222,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7271,7 +7266,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7285,10 +7280,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45086</v>
+        <v>45062</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7301,7 +7296,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7344,7 +7339,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7358,10 +7353,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45274</v>
+        <v>44979</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7373,8 +7368,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7417,7 +7417,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44789</v>
+        <v>45086</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7490,7 +7490,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44957</v>
+        <v>46052</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7519,8 +7519,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7563,7 +7568,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7577,10 +7582,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45272</v>
+        <v>45274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7598,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7636,7 +7641,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7650,10 +7655,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46170</v>
+        <v>44789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7671,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7709,7 +7714,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7723,10 +7728,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45239</v>
+        <v>44957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7738,13 +7743,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45469</v>
+        <v>45272</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7860,7 +7860,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7874,10 +7874,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45610</v>
+        <v>45239</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7889,8 +7889,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7933,7 +7938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7947,10 +7952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45139</v>
+        <v>45469</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8006,7 +8011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8020,10 +8025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46052</v>
+        <v>45610</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8035,13 +8040,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45140</v>
+        <v>45139</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8167,14 +8167,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45184</v>
+        <v>46085</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>3.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45113</v>
+        <v>45140</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45561</v>
+        <v>45184</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45280</v>
+        <v>46210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8449,7 +8449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8463,10 +8463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45196</v>
+        <v>45113</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8522,7 +8522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8532,14 +8532,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46245</v>
+        <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8595,7 +8595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8609,10 +8609,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46245</v>
+        <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8668,7 +8668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45209</v>
+        <v>45196</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8697,13 +8697,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8746,7 +8741,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8760,10 +8755,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46245</v>
+        <v>45209</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8775,8 +8770,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46244</v>
+        <v>45419</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8892,7 +8892,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8906,10 +8906,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45419</v>
+        <v>45028</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8965,7 +8965,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,10 +8979,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45028</v>
+        <v>44979</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9038,7 +9038,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44979</v>
+        <v>44986</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9111,7 +9111,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9121,14 +9121,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46085</v>
+        <v>44680</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9184,7 +9184,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9198,10 +9198,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44986</v>
+        <v>45520</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9257,7 +9257,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44680</v>
+        <v>46237</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9330,7 +9330,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46210</v>
+        <v>46237</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9403,7 +9403,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9417,10 +9417,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45520</v>
+        <v>45189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9476,7 +9476,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9490,10 +9490,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45189</v>
+        <v>45664</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>7.6</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9549,7 +9549,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45664</v>
+        <v>46245</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9639,7 +9639,7 @@
         <v>45610</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9709,10 +9709,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45146</v>
+        <v>46245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9768,7 +9768,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9782,10 +9782,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44574</v>
+        <v>46244</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9797,13 +9797,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9841,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9860,10 +9855,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45779</v>
+        <v>46245</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9871,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9914,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9928,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45789</v>
+        <v>45146</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9948,13 +9943,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9997,7 +9987,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10011,10 +10001,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46237</v>
+        <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10026,8 +10016,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10070,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10084,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46237</v>
+        <v>45779</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10100,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10143,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10157,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45825</v>
+        <v>45789</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10174,11 +10169,11 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10221,7 +10216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10235,10 +10230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45610</v>
+        <v>45825</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10250,8 +10245,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45737</v>
+        <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45869</v>
+        <v>45737</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10457,7 +10457,7 @@
         <v>45869</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45610</v>
+        <v>45869</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5233-2026</t>
+          <t>A 52261-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46049</v>
+        <v>44873</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,120 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Hasselticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 5233-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Spillkråka
@@ -1709,144 +1817,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52261-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44873</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Hasselticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9268-2023</t>
+          <t>A 22716-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44980</v>
+        <v>45789</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1990,17 +1990,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2015,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2024,381 +2029,376 @@
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Stekelbock
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 22716-2025 karta.png", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 22716-2025 georefererad karta.tif", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 22716-2025 FSC-klagomål.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 22716-2025 FSC-klagomål mail.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 22716-2025 tillsynsbegäran.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 22716-2025 tillsynsbegäran mail.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 9268-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>44980</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blodticka
 Mindre märgborre</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9268-2023 artfynd.xlsx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9268-2023 karta.png", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9268-2023 georefererad karta.tif", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9268-2023 FSC-klagomål.docx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9268-2023 FSC-klagomål mail.docx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9268-2023 tillsynsbegäran.docx", "A 9268-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9268-2023 tillsynsbegäran mail.docx", "A 9268-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 62013-2023</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45266</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.6</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Törnskata
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 16309-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44670</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>7.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22716-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45789</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Stekelbock
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 22716-2025 karta.png", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 22716-2025 georefererad karta.tif", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 22716-2025 FSC-klagomål.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 22716-2025 FSC-klagomål mail.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 22716-2025 tillsynsbegäran.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 22716-2025 tillsynsbegäran mail.docx", "A 22716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64189-2023</t>
+          <t>A 47093-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>45196</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 5567-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="D21" s="1" t="n">
+        <v>44960</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 10059-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>17</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 5567-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44960</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Fjällvråk
 Havsörn</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45098</v>
+        <v>45279</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3419,42 +3419,42 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
         <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45279</v>
+        <v>45558</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3821,16 +3821,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>13.1</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,42 +3861,46 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3910,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44979</v>
+        <v>44917</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,13 +3929,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>15.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3943,7 +3942,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3955,10 +3954,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3967,46 +3966,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4020,10 +4019,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46167</v>
+        <v>45098</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4035,13 +4034,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>7.9</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4077,46 +4071,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4130,10 +4124,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45558</v>
+        <v>44965</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4146,17 +4140,17 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4170,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4186,42 +4180,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4231,14 +4225,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45119</v>
+        <v>44979</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4256,7 +4250,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4268,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4280,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4296,46 +4290,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4349,10 +4339,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44917</v>
+        <v>45119</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4364,18 +4354,23 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4389,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4401,46 +4396,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44965</v>
+        <v>46167</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,17 +4464,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>7.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4506,39 +4506,39 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45747</v>
+        <v>45196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45610</v>
+        <v>45789</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5090,8 +5090,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5139,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5153,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45457</v>
+        <v>45113</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5169,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5212,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5226,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>44809</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5242,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>4.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5285,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5290,14 +5295,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45344</v>
+        <v>45419</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5315,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5358,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5367,10 +5372,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44942</v>
+        <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5383,7 +5388,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5431,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5445,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44809</v>
+        <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5455,8 +5460,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5516,7 +5526,7 @@
         <v>45469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5572,7 +5582,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5586,10 +5596,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44979</v>
+        <v>45140</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5601,13 +5611,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>8.1</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5650,7 +5655,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44509</v>
+        <v>44979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5679,13 +5684,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45266</v>
+        <v>44957</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44574</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5896,7 +5896,7 @@
         <v>45196</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5952,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45610</v>
+        <v>44942</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45762</v>
+        <v>44979</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,8 +6054,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>8.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6103,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6108,14 +6113,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44908</v>
+        <v>44602</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6133,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6176,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6190,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44979</v>
+        <v>45928</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6201,7 +6206,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6244,7 +6249,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6258,10 +6263,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45149</v>
+        <v>45469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6274,7 +6279,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6317,7 +6322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45400</v>
+        <v>45935</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6390,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6404,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45928</v>
+        <v>45419</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6420,7 +6425,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6463,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6473,14 +6478,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45935</v>
+        <v>45952</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6493,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6536,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6550,10 +6555,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44602</v>
+        <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6566,7 +6571,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6619,14 +6624,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45952</v>
+        <v>45062</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6639,7 +6644,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6682,7 +6687,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6696,10 +6701,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45419</v>
+        <v>45149</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6712,7 +6717,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6755,7 +6760,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6769,10 +6774,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45280</v>
+        <v>45974</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6785,7 +6790,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6828,7 +6833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6845,7 +6850,7 @@
         <v>45974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6858,7 +6863,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6901,7 +6906,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6915,10 +6920,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45974</v>
+        <v>45209</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6930,8 +6935,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6991,7 +7001,7 @@
         <v>45173</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.2</v>
+        <v>12.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7047,7 +7057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45173</v>
+        <v>45086</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>12.3</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46170</v>
+        <v>45139</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7207,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44941</v>
+        <v>45610</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7266,7 +7276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7280,10 +7290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45062</v>
+        <v>44509</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7295,8 +7305,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7339,7 +7354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7353,10 +7368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44979</v>
+        <v>44735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7368,13 +7383,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7417,7 +7427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7431,10 +7441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45086</v>
+        <v>45274</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7490,7 +7500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7504,10 +7514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46052</v>
+        <v>45457</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7519,13 +7529,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7568,7 +7573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7582,10 +7587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45274</v>
+        <v>45610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7641,7 +7646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7655,10 +7660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44789</v>
+        <v>45825</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7670,8 +7675,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7714,7 +7724,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7728,10 +7738,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44957</v>
+        <v>45280</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7754,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7787,7 +7797,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7801,10 +7811,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45272</v>
+        <v>45239</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7816,8 +7826,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7860,7 +7875,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7874,10 +7889,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45239</v>
+        <v>45266</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7889,13 +7904,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7938,7 +7948,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7948,14 +7958,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45469</v>
+        <v>45344</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7968,7 +7978,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8011,7 +8021,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8025,10 +8035,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45610</v>
+        <v>45173</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8041,7 +8051,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8084,7 +8094,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8098,10 +8108,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45139</v>
+        <v>45272</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8124,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8167,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8167,14 +8177,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46085</v>
+        <v>46052</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8186,8 +8196,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8230,7 +8245,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8244,10 +8259,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45140</v>
+        <v>46245</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8275,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8318,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8317,10 +8332,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45184</v>
+        <v>46244</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8348,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8391,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8390,10 +8405,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8421,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8449,7 +8464,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8463,10 +8478,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45113</v>
+        <v>46245</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8494,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8522,7 +8537,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8532,14 +8547,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45561</v>
+        <v>45610</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8567,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>6.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8595,7 +8610,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8609,10 +8624,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45280</v>
+        <v>45737</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8640,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8668,7 +8683,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8682,10 +8697,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45196</v>
+        <v>44680</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8713,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8741,7 +8756,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8755,10 +8770,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45209</v>
+        <v>45189</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8770,13 +8785,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>7.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8819,7 +8829,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8833,10 +8843,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45419</v>
+        <v>45280</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8849,7 +8859,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.3</v>
+        <v>5.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8892,7 +8902,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8906,10 +8916,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45028</v>
+        <v>45610</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8922,7 +8932,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8965,7 +8975,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,10 +8989,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44979</v>
+        <v>45184</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +9005,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>6.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9038,7 +9048,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9052,10 +9062,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44986</v>
+        <v>45869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9078,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9111,7 +9121,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9125,10 +9135,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44680</v>
+        <v>45869</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9151,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9184,7 +9194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9198,10 +9208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45520</v>
+        <v>45762</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9257,7 +9267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9271,10 +9281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46237</v>
+        <v>45520</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9330,7 +9340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9340,14 +9350,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46237</v>
+        <v>44908</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9403,7 +9413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9417,10 +9427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45189</v>
+        <v>45610</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9476,7 +9486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9490,10 +9500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45664</v>
+        <v>45146</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9549,7 +9559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9563,10 +9573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46245</v>
+        <v>44789</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9622,7 +9632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9636,10 +9646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45610</v>
+        <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9652,7 +9662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9695,7 +9705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9709,10 +9719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46245</v>
+        <v>44986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9725,7 +9735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9768,7 +9778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9782,10 +9792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46244</v>
+        <v>45664</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9798,7 +9808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9841,7 +9851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9855,10 +9865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46245</v>
+        <v>44941</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9871,7 +9881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9914,7 +9924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9924,14 +9934,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45146</v>
+        <v>45561</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9944,7 +9954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9987,7 +9997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10001,10 +10011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44574</v>
+        <v>45747</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10016,13 +10026,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45779</v>
+        <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10094,8 +10099,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10148,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10162,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45789</v>
+        <v>45779</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10167,13 +10177,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10216,7 +10221,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10230,10 +10235,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45825</v>
+        <v>46170</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10245,13 +10250,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10304,14 +10304,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45610</v>
+        <v>46085</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10367,7 +10367,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10381,10 +10381,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45737</v>
+        <v>46210</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45869</v>
+        <v>46237</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45869</v>
+        <v>46237</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52261-2022</t>
+          <t>A 5233-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44873</v>
+        <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,124 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52261-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44873</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
@@ -1709,144 +1821,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 5233-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22716-2025</t>
+          <t>A 9268-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45789</v>
+        <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1990,22 +1990,17 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2020,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2029,376 +2024,381 @@
         <v>3</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blodticka
+Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9268-2023 artfynd.xlsx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9268-2023 karta.png", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9268-2023 georefererad karta.tif", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9268-2023 FSC-klagomål.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9268-2023 FSC-klagomål mail.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9268-2023 tillsynsbegäran.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9268-2023 tillsynsbegäran mail.docx", "A 9268-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 62013-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Törnskata
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 16309-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44670</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22716-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45789</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Stekelbock
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 22716-2025 karta.png", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 22716-2025 georefererad karta.tif", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 22716-2025 FSC-klagomål.docx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 22716-2025 FSC-klagomål mail.docx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 22716-2025 tillsynsbegäran.docx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 22716-2025 tillsynsbegäran mail.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 9268-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44980</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blodticka
-Mindre märgborre</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9268-2023 artfynd.xlsx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9268-2023 karta.png", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9268-2023 georefererad karta.tif", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9268-2023 FSC-klagomål.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9268-2023 FSC-klagomål mail.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9268-2023 tillsynsbegäran.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9268-2023 tillsynsbegäran mail.docx", "A 9268-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 62013-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45266</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Törnskata
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 16309-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44670</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 47093-2023</t>
+          <t>A 64189-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45196</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 5567-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44960</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Sårläka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>Hasselticka
 Myskmadra</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="D26" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 5567-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44960</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W23">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45279</v>
+        <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3419,42 +3419,42 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
         <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45558</v>
+        <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3711,13 +3711,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3821,17 +3821,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.4</v>
+        <v>13.1</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,46 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3910,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44917</v>
+        <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3929,8 +3925,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>15.8</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3942,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3954,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3966,46 +3967,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4019,10 +4020,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45098</v>
+        <v>45558</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4035,10 +4036,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -4075,42 +4076,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4124,10 +4125,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4139,17 +4140,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -4164,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4180,42 +4186,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4225,14 +4235,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44979</v>
+        <v>46167</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4250,19 +4260,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4274,10 +4284,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4286,46 +4296,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4339,10 +4349,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45119</v>
+        <v>44917</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,22 +4364,17 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>13.1</v>
+        <v>15.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4384,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4396,46 +4401,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46167</v>
+        <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4464,37 +4469,32 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4506,39 +4506,39 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45196</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45789</v>
+        <v>45747</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5090,13 +5090,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5139,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5153,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45113</v>
+        <v>45457</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5169,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5212,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5226,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44809</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5242,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5285,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5295,14 +5290,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45419</v>
+        <v>45344</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5315,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5358,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5372,10 +5367,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44979</v>
+        <v>44942</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5388,7 +5383,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5431,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44574</v>
+        <v>44809</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5460,13 +5455,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5526,7 +5516,7 @@
         <v>45469</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5582,7 +5572,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5596,10 +5586,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45140</v>
+        <v>44979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5611,8 +5601,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>8.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5655,7 +5650,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>44509</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5684,8 +5679,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44957</v>
+        <v>45266</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5801,7 +5801,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5815,10 +5815,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>45869</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5830,13 +5830,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5874,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5888,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45196</v>
+        <v>45869</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5909,7 +5904,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5947,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5961,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44942</v>
+        <v>44574</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5981,8 +5976,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44979</v>
+        <v>45196</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,13 +6054,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6103,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44602</v>
+        <v>45610</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6133,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6176,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6190,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45928</v>
+        <v>44979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6206,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6249,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6263,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45469</v>
+        <v>45762</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6279,7 +6274,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6322,7 +6317,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6336,10 +6331,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45935</v>
+        <v>45149</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6352,7 +6347,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6390,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6404,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45419</v>
+        <v>45400</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6425,7 +6420,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6468,7 +6463,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6478,14 +6473,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45952</v>
+        <v>45928</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6493,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6536,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6551,14 +6546,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45400</v>
+        <v>44908</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6571,7 +6566,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6614,7 +6609,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6628,10 +6623,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45062</v>
+        <v>45935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6644,7 +6639,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6687,7 +6682,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6701,10 +6696,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45149</v>
+        <v>44602</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6717,7 +6712,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6760,7 +6755,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45974</v>
+        <v>45419</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6790,7 +6785,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6833,7 +6828,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6847,10 +6842,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45974</v>
+        <v>45280</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6863,7 +6858,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6906,7 +6901,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6916,14 +6911,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45209</v>
+        <v>45952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6935,13 +6930,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6984,7 +6974,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7001,7 +6991,7 @@
         <v>45173</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7014,7 +7004,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>12.3</v>
+        <v>6.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7057,7 +7047,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45086</v>
+        <v>45173</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>12.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45139</v>
+        <v>45974</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45610</v>
+        <v>45974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7233,7 +7223,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7276,7 +7266,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7290,10 +7280,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44509</v>
+        <v>44941</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7305,13 +7295,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7354,7 +7339,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7368,10 +7353,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44735</v>
+        <v>45062</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7384,7 +7369,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7427,7 +7412,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7441,10 +7426,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45274</v>
+        <v>44979</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7456,8 +7441,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7500,7 +7490,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7514,10 +7504,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45457</v>
+        <v>45086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7530,7 +7520,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7573,7 +7563,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7587,10 +7577,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45610</v>
+        <v>45274</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7646,7 +7636,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7660,10 +7650,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45825</v>
+        <v>44789</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7675,13 +7665,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7724,7 +7709,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7738,10 +7723,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45280</v>
+        <v>44957</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7754,7 +7739,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7797,7 +7782,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7811,10 +7796,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45239</v>
+        <v>45272</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7826,13 +7811,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7875,7 +7855,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7889,10 +7869,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45266</v>
+        <v>46052</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7904,8 +7884,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7948,7 +7933,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7958,14 +7943,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45344</v>
+        <v>46170</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7978,7 +7963,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8021,7 +8006,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8035,10 +8020,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45173</v>
+        <v>45239</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8050,8 +8035,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8094,7 +8084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8108,10 +8098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45272</v>
+        <v>45469</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8124,7 +8114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8167,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8181,10 +8171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46052</v>
+        <v>45610</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8196,13 +8186,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8245,7 +8230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8259,10 +8244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46245</v>
+        <v>45139</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8275,7 +8260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8318,7 +8303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8332,10 +8317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46244</v>
+        <v>45140</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8348,7 +8333,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8391,7 +8376,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8405,10 +8390,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46245</v>
+        <v>45184</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8421,7 +8406,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8464,7 +8449,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8478,10 +8463,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46245</v>
+        <v>45113</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8494,7 +8479,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8537,7 +8522,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8547,14 +8532,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45610</v>
+        <v>45561</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8567,7 +8552,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8610,7 +8595,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8624,10 +8609,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45737</v>
+        <v>45280</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8640,7 +8625,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8683,7 +8668,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8693,14 +8678,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44680</v>
+        <v>46085</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8713,7 +8698,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8756,7 +8741,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8770,10 +8755,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45189</v>
+        <v>45196</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8786,7 +8771,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.6</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8829,7 +8814,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8843,10 +8828,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45280</v>
+        <v>46210</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8859,7 +8844,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.6</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8902,7 +8887,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8916,10 +8901,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45610</v>
+        <v>45209</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8931,8 +8916,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8975,7 +8965,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8989,10 +8979,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45184</v>
+        <v>45419</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9005,7 +8995,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.8</v>
+        <v>0.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9048,7 +9038,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9062,10 +9052,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45869</v>
+        <v>45028</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9078,7 +9068,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9121,7 +9111,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9135,10 +9125,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45869</v>
+        <v>44979</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9151,7 +9141,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9194,7 +9184,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9208,10 +9198,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45762</v>
+        <v>44986</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9224,7 +9214,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9267,7 +9257,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9281,10 +9271,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45520</v>
+        <v>44680</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9297,7 +9287,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9340,7 +9330,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9350,14 +9340,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44908</v>
+        <v>45520</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9370,7 +9360,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9413,7 +9403,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9427,10 +9417,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45610</v>
+        <v>45189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9443,7 +9433,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9486,7 +9476,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9500,10 +9490,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45146</v>
+        <v>45664</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9516,7 +9506,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9559,7 +9549,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9573,10 +9563,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44789</v>
+        <v>45610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9589,7 +9579,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9632,7 +9622,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9646,10 +9636,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45028</v>
+        <v>45146</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9662,7 +9652,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9705,7 +9695,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9719,10 +9709,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44986</v>
+        <v>46237</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9735,7 +9725,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9778,7 +9768,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9792,10 +9782,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45664</v>
+        <v>46237</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9808,7 +9798,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9851,7 +9841,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9865,10 +9855,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44941</v>
+        <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9880,8 +9870,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9924,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9934,14 +9929,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45561</v>
+        <v>45779</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9954,7 +9949,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9997,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10011,10 +10006,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45747</v>
+        <v>45789</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10026,8 +10021,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10070,7 +10070,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44574</v>
+        <v>46244</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10099,13 +10099,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10148,7 +10143,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10162,10 +10157,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45779</v>
+        <v>46245</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10178,7 +10173,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10221,7 +10216,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10235,10 +10230,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46170</v>
+        <v>46245</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10294,7 +10289,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10304,14 +10299,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46085</v>
+        <v>46245</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10319,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10367,7 +10362,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10381,10 +10376,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46210</v>
+        <v>45825</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10396,8 +10391,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10440,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10454,10 +10454,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46237</v>
+        <v>45610</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46237</v>
+        <v>45737</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64189-2023</t>
+          <t>A 5567-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Sårläka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="D24" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 10059-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>17</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 5567-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44960</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45098</v>
+        <v>44917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>15.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3422,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>45279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,19 +3490,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3536,42 +3531,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45119</v>
+        <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3606,13 +3601,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12.4</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3639,49 +3634,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45279</v>
+        <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,14 +3705,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,42 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44979</v>
+        <v>45558</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,25 +3925,20 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3955,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3971,42 +3966,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4020,10 +4015,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45558</v>
+        <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4035,14 +4030,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4076,42 +4076,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4125,10 +4129,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45119</v>
+        <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,19 +4144,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4186,46 +4185,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4239,10 +4234,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46167</v>
+        <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4254,37 +4249,32 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
         <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4296,46 +4286,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4345,14 +4335,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44917</v>
+        <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4364,8 +4354,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>15.8</v>
+        <v>2.7</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4377,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4389,10 +4384,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4401,46 +4396,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,8 +4464,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>13.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4510,35 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45747</v>
+        <v>45419</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45457</v>
+        <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5290,14 +5290,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45344</v>
+        <v>44957</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5367,10 +5367,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44942</v>
+        <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44809</v>
+        <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5455,8 +5455,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5499,7 +5504,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5513,10 +5518,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45469</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5528,8 +5533,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5572,7 +5582,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5586,10 +5596,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44979</v>
+        <v>44602</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5601,13 +5611,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>8.1</v>
+        <v>4.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5650,7 +5655,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5664,10 +5669,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44509</v>
+        <v>46052</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5681,11 +5686,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5728,7 +5733,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5742,10 +5747,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45266</v>
+        <v>45928</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5758,7 +5763,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5801,7 +5806,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5815,10 +5820,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45869</v>
+        <v>45935</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5831,7 +5836,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5874,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5888,10 +5893,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45869</v>
+        <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5947,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5957,14 +5962,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44574</v>
+        <v>45952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5976,13 +5981,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45196</v>
+        <v>45086</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45610</v>
+        <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44979</v>
+        <v>45610</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6244,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6258,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45762</v>
+        <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6273,8 +6273,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>11</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6317,7 +6322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6331,10 +6336,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45149</v>
+        <v>45974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6347,7 +6352,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6390,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6404,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45400</v>
+        <v>45974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6420,7 +6425,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6463,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6477,10 +6482,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45928</v>
+        <v>45457</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6493,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6536,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6546,14 +6551,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44908</v>
+        <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6566,7 +6571,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6609,7 +6614,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6623,10 +6628,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45935</v>
+        <v>45762</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6639,7 +6644,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6682,7 +6687,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6692,14 +6697,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44602</v>
+        <v>44908</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6712,7 +6717,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6755,7 +6760,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6769,10 +6774,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45419</v>
+        <v>45196</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6785,7 +6790,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6828,7 +6833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6842,10 +6847,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45280</v>
+        <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6858,7 +6863,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5.6</v>
+        <v>1.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6901,7 +6906,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6911,14 +6916,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45952</v>
+        <v>45825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6930,8 +6935,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45173</v>
+        <v>45140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7047,7 +7057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45173</v>
+        <v>45610</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>12.3</v>
+        <v>6.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45974</v>
+        <v>45737</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7207,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45974</v>
+        <v>44979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7222,8 +7232,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>3.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7266,7 +7281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7280,10 +7295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44941</v>
+        <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7339,7 +7354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7353,10 +7368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45062</v>
+        <v>46170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7369,7 +7384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7412,7 +7427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7426,10 +7441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44979</v>
+        <v>44942</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7441,13 +7456,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7490,7 +7500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7504,10 +7514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45086</v>
+        <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7563,7 +7573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7577,10 +7587,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45274</v>
+        <v>45869</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7636,7 +7646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7650,10 +7660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44789</v>
+        <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7709,7 +7719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7723,10 +7733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44957</v>
+        <v>45419</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7739,7 +7749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7782,7 +7792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7796,10 +7806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45272</v>
+        <v>45610</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7812,7 +7822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>5.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7855,7 +7865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7865,14 +7875,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46052</v>
+        <v>46085</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7884,13 +7894,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7933,7 +7938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7947,10 +7952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46170</v>
+        <v>45062</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8006,7 +8011,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8020,10 +8025,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45239</v>
+        <v>46210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8035,13 +8040,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>5.2</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8098,10 +8098,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45469</v>
+        <v>45149</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8171,10 +8171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45610</v>
+        <v>45209</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8186,8 +8186,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8230,7 +8235,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8244,10 +8249,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45139</v>
+        <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8265,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>12.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8308,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8317,10 +8322,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45140</v>
+        <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8338,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8381,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8390,10 +8395,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45184</v>
+        <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8411,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8449,7 +8454,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8463,10 +8468,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45113</v>
+        <v>45280</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8484,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8522,7 +8527,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8532,14 +8537,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45561</v>
+        <v>45239</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8551,8 +8556,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8595,7 +8605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8609,10 +8619,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45280</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8668,7 +8678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8682,10 +8692,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46085</v>
+        <v>45344</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8741,7 +8751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8755,10 +8765,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45196</v>
+        <v>45173</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8771,7 +8781,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8814,7 +8824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8828,10 +8838,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46210</v>
+        <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8844,7 +8854,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8887,7 +8897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8901,10 +8911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45209</v>
+        <v>46237</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8916,13 +8926,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8965,7 +8970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8979,10 +8984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45419</v>
+        <v>46237</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +9000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9038,7 +9043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9052,10 +9057,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45028</v>
+        <v>46245</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9111,7 +9116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9125,10 +9130,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44979</v>
+        <v>46244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9146,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9184,7 +9189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9198,10 +9203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44986</v>
+        <v>46245</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9219,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9257,7 +9262,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9271,10 +9276,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44680</v>
+        <v>46245</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9292,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9330,7 +9335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9344,10 +9349,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45520</v>
+        <v>44680</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9420,7 +9425,7 @@
         <v>45189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9476,7 +9481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9490,10 +9495,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45664</v>
+        <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9566,7 +9571,7 @@
         <v>45610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9622,7 +9627,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9636,10 +9641,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45146</v>
+        <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9652,7 +9657,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9695,7 +9700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9709,10 +9714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46237</v>
+        <v>45520</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9725,7 +9730,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9768,7 +9773,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9782,10 +9787,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46237</v>
+        <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9841,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9855,10 +9860,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44574</v>
+        <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9870,13 +9875,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45779</v>
+        <v>45028</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45789</v>
+        <v>44986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10021,13 +10021,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10070,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10084,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46244</v>
+        <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10100,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10143,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10157,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46245</v>
+        <v>44941</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10173,7 +10168,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10216,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10226,14 +10221,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46245</v>
+        <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10289,7 +10284,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10303,10 +10298,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46245</v>
+        <v>45747</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10319,7 +10314,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10362,7 +10357,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10376,10 +10371,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45825</v>
+        <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10393,11 +10388,11 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10440,7 +10435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10454,10 +10449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45610</v>
+        <v>45779</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45737</v>
+        <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10542,8 +10537,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>44979</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45196</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44937</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45131</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45211</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44621</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45558</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45419</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44957</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44602</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46052</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45928</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45935</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45086</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45610</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>45974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>45457</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45762</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>44908</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45196</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>45610</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45737</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44942</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45869</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45419</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45610</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>46085</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45062</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>46210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45149</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45209</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45280</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45239</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45344</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45173</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>46237</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>46237</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>46245</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>46244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>46245</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>46245</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44680</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45520</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45028</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44941</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45747</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45779</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>44979</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>45196</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>44937</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>45279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45131</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45211</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44621</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>44917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45558</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
         <v>45419</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         <v>44957</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44602</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46052</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45928</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45935</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5896,7 +5896,7 @@
         <v>45400</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45952</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>45086</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>45610</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45974</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>45974</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>45457</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45610</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         <v>45762</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>44908</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45196</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>45113</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>45825</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45140</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>45610</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45737</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44979</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>45196</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46170</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44942</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>45869</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45869</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45419</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45610</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>46085</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>45062</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>46210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45149</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>45209</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45274</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45280</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>45239</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45344</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45173</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>46237</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>46237</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>46245</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>46244</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>46245</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>46245</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>44680</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>45189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45280</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         <v>45610</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         <v>45520</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>45028</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10009,7 +10009,7 @@
         <v>44986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44941</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45747</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45779</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62013-2023</t>
+          <t>A 22716-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45266</v>
+        <v>45789</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,14 +2097,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2131,274 +2136,269 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Stekelbock
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 22716-2025 karta.png", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 22716-2025 georefererad karta.tif", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 22716-2025 FSC-klagomål.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 22716-2025 FSC-klagomål mail.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 22716-2025 tillsynsbegäran.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 22716-2025 tillsynsbegäran mail.docx", "A 22716-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 62013-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Skogsknipprot
 Törnskata
 Gullviva</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 16309-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>44670</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>7.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22716-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45789</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Björksplintborre
-Stekelbock
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 22716-2025 karta.png", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 22716-2025 georefererad karta.tif", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 22716-2025 FSC-klagomål.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 22716-2025 FSC-klagomål mail.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 22716-2025 tillsynsbegäran.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 22716-2025 tillsynsbegäran mail.docx", "A 22716-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 5567-2023</t>
+          <t>A 64189-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44960</v>
+        <v>45279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>10.1</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 5567-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44960</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>Sårläka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 8939-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44979</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>2.7</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44917</v>
+        <v>45098</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>15.8</v>
+        <v>1.2</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3422,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45279</v>
+        <v>45118</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,14 +3490,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3531,42 +3536,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45118</v>
+        <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,13 +3606,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>12.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3634,49 +3639,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3690,10 +3695,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46167</v>
+        <v>45279</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3705,19 +3710,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3803,7 +3803,7 @@
         <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,42 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3906,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45558</v>
+        <v>44979</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3925,21 +3925,26 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -3950,10 +3955,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3966,42 +3971,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4015,10 +4020,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45119</v>
+        <v>45558</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4030,19 +4035,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4076,46 +4076,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,10 +4125,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45098</v>
+        <v>45119</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4144,14 +4140,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4185,42 +4186,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4234,10 +4239,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44965</v>
+        <v>44917</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4250,16 +4255,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>15.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4274,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4286,46 +4291,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4335,14 +4340,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44979</v>
+        <v>46167</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4360,19 +4365,19 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4384,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4396,46 +4401,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4449,10 +4454,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45119</v>
+        <v>44965</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4464,13 +4469,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>13.1</v>
+        <v>1.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4510,35 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44809</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45419</v>
+        <v>45747</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45469</v>
+        <v>45457</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44979</v>
+        <v>44735</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44957</v>
+        <v>45789</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5309,8 +5309,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5370,7 +5375,7 @@
         <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5443,7 +5448,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5504,7 +5509,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5514,14 +5519,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44979</v>
+        <v>45344</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5533,13 +5538,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>8.1</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44602</v>
+        <v>44942</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46052</v>
+        <v>44809</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5684,13 +5684,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5733,7 +5728,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5747,10 +5742,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45928</v>
+        <v>45825</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5762,8 +5757,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45935</v>
+        <v>45928</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45400</v>
+        <v>45469</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5962,14 +5962,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45952</v>
+        <v>45935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45086</v>
+        <v>44979</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,8 +6054,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>8.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6103,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6117,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45139</v>
+        <v>45610</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6133,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6176,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6190,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45610</v>
+        <v>45737</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6201,7 +6206,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6244,7 +6249,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6254,14 +6259,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44509</v>
+        <v>45952</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6273,13 +6278,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45974</v>
+        <v>45869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45974</v>
+        <v>45869</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6468,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45457</v>
+        <v>45610</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45610</v>
+        <v>44509</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6570,8 +6570,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6614,7 +6619,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6628,10 +6633,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45762</v>
+        <v>45974</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6644,7 +6649,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6687,7 +6692,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6697,14 +6702,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44908</v>
+        <v>45974</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6717,7 +6722,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6760,7 +6765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6774,10 +6779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45196</v>
+        <v>45266</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6790,7 +6795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6833,7 +6838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6847,10 +6852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45113</v>
+        <v>45196</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6863,7 +6868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6906,7 +6911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6920,10 +6925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45825</v>
+        <v>46052</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6937,11 +6942,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6984,7 +6989,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6998,10 +7003,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45140</v>
+        <v>45149</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7014,7 +7019,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7057,7 +7062,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7071,10 +7076,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45610</v>
+        <v>45400</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7087,7 +7092,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7130,7 +7135,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7144,10 +7149,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45737</v>
+        <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7160,7 +7165,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7203,7 +7208,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7217,10 +7222,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44979</v>
+        <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7232,13 +7237,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7281,7 +7281,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45196</v>
+        <v>45280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7368,10 +7368,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46170</v>
+        <v>45173</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7427,7 +7427,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44942</v>
+        <v>45173</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7500,7 +7500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7514,10 +7514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45869</v>
+        <v>45762</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45869</v>
+        <v>44908</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45469</v>
+        <v>44941</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45419</v>
+        <v>45062</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7792,7 +7792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45610</v>
+        <v>44979</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7821,8 +7821,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7865,7 +7870,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7875,14 +7880,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46085</v>
+        <v>45086</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7895,7 +7900,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7938,7 +7943,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7952,10 +7957,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45062</v>
+        <v>45274</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7968,7 +7973,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8011,7 +8016,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8025,10 +8030,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46210</v>
+        <v>44789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8041,7 +8046,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8084,7 +8089,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8098,10 +8103,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45149</v>
+        <v>44957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8119,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8162,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8171,10 +8176,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45209</v>
+        <v>45272</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8186,13 +8191,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8235,7 +8235,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8249,10 +8249,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45173</v>
+        <v>45239</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8264,8 +8264,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>12.3</v>
+        <v>5.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8308,7 +8313,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8322,10 +8327,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44735</v>
+        <v>45469</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8338,7 +8343,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8381,7 +8386,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8395,10 +8400,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45274</v>
+        <v>45610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8411,7 +8416,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8454,7 +8459,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8468,10 +8473,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45280</v>
+        <v>46170</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8484,7 +8489,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8527,7 +8532,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8541,10 +8546,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45239</v>
+        <v>45139</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8556,13 +8561,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>5.2</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45266</v>
+        <v>45140</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8678,7 +8678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8688,14 +8688,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45344</v>
+        <v>45184</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45173</v>
+        <v>45113</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8824,7 +8824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45272</v>
+        <v>45561</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46237</v>
+        <v>45280</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46237</v>
+        <v>45196</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9043,7 +9043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46245</v>
+        <v>46085</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9116,7 +9116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46244</v>
+        <v>45209</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9145,8 +9145,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9189,7 +9194,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9203,10 +9208,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46245</v>
+        <v>46210</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9219,7 +9224,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9262,7 +9267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9276,10 +9281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46245</v>
+        <v>45419</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9292,7 +9297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.8</v>
+        <v>0.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9335,7 +9340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9349,10 +9354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44680</v>
+        <v>45028</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9365,7 +9370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9408,7 +9413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9422,10 +9427,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45189</v>
+        <v>44979</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9438,7 +9443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>7.6</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9481,7 +9486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9495,10 +9500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45280</v>
+        <v>44986</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9554,7 +9559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9568,10 +9573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45610</v>
+        <v>44680</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9584,7 +9589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9627,7 +9632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9641,10 +9646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45184</v>
+        <v>45520</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9657,7 +9662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9700,7 +9705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9714,10 +9719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45520</v>
+        <v>45189</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9735,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.2</v>
+        <v>7.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9773,7 +9778,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9787,10 +9792,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45146</v>
+        <v>45664</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9808,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9851,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9860,10 +9865,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44789</v>
+        <v>45610</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9881,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9924,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9938,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45028</v>
+        <v>45146</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9954,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +9997,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10011,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44986</v>
+        <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10021,8 +10026,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10075,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10089,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45664</v>
+        <v>45779</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10105,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10148,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10162,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44941</v>
+        <v>46237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10178,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10211,7 +10221,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10221,14 +10231,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45561</v>
+        <v>46237</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10251,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10284,7 +10294,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10298,10 +10308,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45747</v>
+        <v>46244</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10324,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10357,7 +10367,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10371,10 +10381,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44574</v>
+        <v>46245</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10384,11 +10394,6 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -10435,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10449,10 +10454,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45779</v>
+        <v>46245</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10465,7 +10470,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10508,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10522,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45789</v>
+        <v>46245</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10537,13 +10542,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>46125</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>45846</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>46188</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 22716-2025</t>
+          <t>A 62013-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45789</v>
+        <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,19 +2097,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2136,269 +2131,274 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skogsknipprot
+Törnskata
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 16309-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44670</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22716-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45789</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Björksplintborre
 Stekelbock
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 22716-2025 karta.png", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 22716-2025 georefererad karta.tif", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 22716-2025 FSC-klagomål.docx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 22716-2025 FSC-klagomål mail.docx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 22716-2025 tillsynsbegäran.docx", "A 22716-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 22716-2025 tillsynsbegäran mail.docx", "A 22716-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 62013-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45266</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Skogsknipprot
-Törnskata
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62013-2023 artfynd.xlsx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62013-2023 karta.png", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62013-2023 georefererad karta.tif", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62013-2023 FSC-klagomål.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62013-2023 FSC-klagomål mail.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62013-2023 tillsynsbegäran.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62013-2023 tillsynsbegäran mail.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 62013-2023 prioriterade fågelarter.docx", "A 62013-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 16309-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44670</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 16309-2022 artfynd.xlsx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 16309-2022 karta.png", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 16309-2022 georefererad karta.tif", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 16309-2022 FSC-klagomål.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 16309-2022 FSC-klagomål mail.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 16309-2022 tillsynsbegäran.docx", "A 16309-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 16309-2022 tillsynsbegäran mail.docx", "A 16309-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 64189-2023</t>
+          <t>A 5567-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45279</v>
+        <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>10.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2468,895 +2468,895 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
+          <t>Sårläka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 12033-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Blåsippa
 Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J19" t="n">
+      <c r="D24" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 10059-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>17</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 5567-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>44960</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Sårläka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5567-2023 artfynd.xlsx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5567-2023 karta.png", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5567-2023 georefererad karta.tif", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5567-2023 FSC-klagomål.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5567-2023 FSC-klagomål mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5567-2023 tillsynsbegäran.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5567-2023 tillsynsbegäran mail.docx", "A 5567-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45098</v>
+        <v>44917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3386,13 +3386,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.2</v>
+        <v>15.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -3422,46 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45118</v>
+        <v>45279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,19 +3490,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -3536,42 +3531,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45119</v>
+        <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3606,13 +3601,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>12.4</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -3639,49 +3634,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,10 +3690,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45279</v>
+        <v>45119</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3710,11 +3705,16 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3744,49 +3744,49 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45119</v>
+        <v>45558</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3815,22 +3815,17 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>13.1</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3845,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3861,42 +3856,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3906,14 +3901,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44979</v>
+        <v>45119</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3931,7 +3926,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3943,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3955,10 +3950,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3971,42 +3966,46 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4020,10 +4019,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45558</v>
+        <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4035,11 +4034,16 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.7</v>
+        <v>7.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -4072,46 +4076,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4125,10 +4129,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45119</v>
+        <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4140,19 +4144,14 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4186,46 +4185,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4239,10 +4234,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44917</v>
+        <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4255,17 +4250,17 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>15.8</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4279,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4291,46 +4286,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4340,14 +4335,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46167</v>
+        <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4365,20 +4360,20 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.9</v>
+        <v>2.7</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -4389,10 +4384,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4401,46 +4396,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4454,10 +4449,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4469,8 +4464,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.8</v>
+        <v>13.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4510,35 +4510,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45747</v>
+        <v>45419</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45457</v>
+        <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44735</v>
+        <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45789</v>
+        <v>44957</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5309,13 +5309,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5375,7 +5370,7 @@
         <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5448,7 +5443,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5509,7 +5504,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5519,14 +5514,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45344</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5538,8 +5533,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>8.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5596,10 +5596,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44942</v>
+        <v>44602</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44809</v>
+        <v>45825</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5684,8 +5684,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5728,7 +5733,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5742,10 +5747,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45825</v>
+        <v>45928</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5757,13 +5762,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45928</v>
+        <v>45610</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5893,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45469</v>
+        <v>45737</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45935</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44979</v>
+        <v>45400</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,13 +6054,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>8.1</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6103,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6117,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45610</v>
+        <v>45869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6133,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6176,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6190,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45737</v>
+        <v>45869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6206,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6249,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6259,14 +6254,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45952</v>
+        <v>46052</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6278,8 +6273,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45869</v>
+        <v>45952</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6395,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45869</v>
+        <v>45610</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6468,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45610</v>
+        <v>45086</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44509</v>
+        <v>45139</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6570,13 +6570,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6619,7 +6614,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6633,10 +6628,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45974</v>
+        <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6649,7 +6644,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6692,7 +6687,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6706,10 +6701,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45974</v>
+        <v>44509</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6721,8 +6716,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45266</v>
+        <v>45974</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6852,10 +6852,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45196</v>
+        <v>45974</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6911,7 +6911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6925,10 +6925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46052</v>
+        <v>45457</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6940,13 +6940,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6989,7 +6984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7003,10 +6998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45149</v>
+        <v>45610</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7019,7 +7014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7062,7 +7057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7076,10 +7071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45400</v>
+        <v>45196</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7092,7 +7087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7135,7 +7130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7149,10 +7144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44602</v>
+        <v>45113</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7165,7 +7160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7208,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7222,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45419</v>
+        <v>45762</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7238,7 +7233,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4</v>
+        <v>11</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7281,7 +7276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7295,10 +7290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45280</v>
+        <v>45140</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7311,7 +7306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7354,7 +7349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7364,14 +7359,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45173</v>
+        <v>44908</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7384,7 +7379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7427,7 +7422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7441,10 +7436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45173</v>
+        <v>44979</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7456,8 +7451,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>12.3</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7500,7 +7500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7514,10 +7514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45762</v>
+        <v>45196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>11</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7573,7 +7573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7583,14 +7583,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44908</v>
+        <v>44942</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44941</v>
+        <v>45469</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45062</v>
+        <v>45419</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7792,7 +7792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7806,10 +7806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44979</v>
+        <v>45062</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7821,13 +7821,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7870,7 +7865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7884,10 +7879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45086</v>
+        <v>45149</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7900,7 +7895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7943,7 +7938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7957,10 +7952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45274</v>
+        <v>45209</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7972,8 +7967,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8016,7 +8016,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8030,10 +8030,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44789</v>
+        <v>45173</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.3</v>
+        <v>12.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8089,7 +8089,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8103,10 +8103,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44957</v>
+        <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8162,7 +8162,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8176,10 +8176,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45272</v>
+        <v>45274</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8235,7 +8235,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8249,10 +8249,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45239</v>
+        <v>46170</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8264,13 +8264,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8313,7 +8308,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8327,10 +8322,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45469</v>
+        <v>45280</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8343,7 +8338,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8386,7 +8381,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8400,10 +8395,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45610</v>
+        <v>45239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8415,8 +8410,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8473,10 +8473,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46170</v>
+        <v>45266</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8532,7 +8532,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8542,14 +8542,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45139</v>
+        <v>45344</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8619,10 +8619,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45140</v>
+        <v>45173</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8678,7 +8678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45184</v>
+        <v>45272</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8751,7 +8751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45113</v>
+        <v>46085</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8824,7 +8824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8834,14 +8834,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45561</v>
+        <v>46210</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45280</v>
+        <v>44680</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45196</v>
+        <v>45189</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>7.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9043,7 +9043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9053,14 +9053,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46085</v>
+        <v>45280</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9116,7 +9116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45209</v>
+        <v>45610</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9145,13 +9145,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9194,7 +9189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9208,10 +9203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46210</v>
+        <v>45184</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9224,7 +9219,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>6.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9267,7 +9262,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9281,10 +9276,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45419</v>
+        <v>45520</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9297,7 +9292,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9340,7 +9335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9354,10 +9349,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45028</v>
+        <v>45146</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9370,7 +9365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9413,7 +9408,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9427,10 +9422,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44979</v>
+        <v>44789</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9443,7 +9438,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9486,7 +9481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9500,10 +9495,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44986</v>
+        <v>46237</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9516,7 +9511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9559,7 +9554,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9573,10 +9568,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44680</v>
+        <v>46237</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9589,7 +9584,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9632,7 +9627,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9646,10 +9641,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45520</v>
+        <v>45028</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9662,7 +9657,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9705,7 +9700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9719,10 +9714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45189</v>
+        <v>44986</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9735,7 +9730,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7.6</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9795,7 +9790,7 @@
         <v>45664</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9851,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9865,10 +9860,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45610</v>
+        <v>44941</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9881,7 +9876,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9924,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9938,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45146</v>
+        <v>46245</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9954,7 +9949,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9997,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10007,14 +10002,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44574</v>
+        <v>45561</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10026,13 +10021,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10075,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10089,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45779</v>
+        <v>45747</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10105,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10148,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10162,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10178,7 +10168,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10221,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10235,10 +10225,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10251,7 +10241,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10294,7 +10284,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10308,10 +10298,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10314,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10367,7 +10357,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10381,10 +10371,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46245</v>
+        <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10394,6 +10384,11 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -10440,7 +10435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10454,10 +10449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46245</v>
+        <v>45779</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46245</v>
+        <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10542,8 +10537,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 18378-2026</t>
+          <t>A 34573-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46125</v>
+        <v>45846</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -1245,10 +1245,10 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
@@ -1262,38 +1262,38 @@
         </is>
       </c>
       <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 18378-2026 artfynd.xlsx", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 34573-2025 artfynd.xlsx", "A 34573-2025")</f>
         <v/>
       </c>
       <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 18378-2026 karta.png", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 34573-2025 karta.png", "A 34573-2025")</f>
         <v/>
       </c>
       <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 18378-2026 georefererad karta.tif", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 34573-2025 georefererad karta.tif", "A 34573-2025")</f>
         <v/>
       </c>
       <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 18378-2026 FSC-klagomål.docx", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 34573-2025 FSC-klagomål.docx", "A 34573-2025")</f>
         <v/>
       </c>
       <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 18378-2026 FSC-klagomål mail.docx", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 34573-2025 FSC-klagomål mail.docx", "A 34573-2025")</f>
         <v/>
       </c>
       <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 18378-2026 tillsynsbegäran.docx", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 34573-2025 tillsynsbegäran.docx", "A 34573-2025")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 18378-2026 tillsynsbegäran mail.docx", "A 18378-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 34573-2025 tillsynsbegäran mail.docx", "A 34573-2025")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 34573-2025</t>
+          <t>A 27135-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45846</v>
+        <v>46188</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1320,28 +1320,23 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>7.3</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -1352,21 +1347,137 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
         <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>7</v>
       </c>
       <c r="T8" t="n">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Skogskorn
+Jungfrulin
+Ängsskära
+Myskmadra
+Skogsknipprot
+Strävlosta
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27135-2026 artfynd.xlsx", "A 27135-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27135-2026 karta.png", "A 27135-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27135-2026 georefererad karta.tif", "A 27135-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27135-2026 FSC-klagomål.docx", "A 27135-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27135-2026 FSC-klagomål mail.docx", "A 27135-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27135-2026 tillsynsbegäran.docx", "A 27135-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27135-2026 tillsynsbegäran mail.docx", "A 27135-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 18378-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="n">
+        <v>65</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Jungfrulin
 Noshornsoxe
@@ -1377,143 +1488,32 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 34573-2025 artfynd.xlsx", "A 34573-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 34573-2025 karta.png", "A 34573-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 34573-2025 georefererad karta.tif", "A 34573-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 34573-2025 FSC-klagomål.docx", "A 34573-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 34573-2025 FSC-klagomål mail.docx", "A 34573-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 34573-2025 tillsynsbegäran.docx", "A 34573-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 34573-2025 tillsynsbegäran mail.docx", "A 34573-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 27135-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>16</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Skogskorn
-Jungfrulin
-Ängsskära
-Myskmadra
-Skogsknipprot
-Strävlosta
-Blåsippa</t>
-        </is>
-      </c>
       <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27135-2026 artfynd.xlsx", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 18378-2026 artfynd.xlsx", "A 18378-2026")</f>
         <v/>
       </c>
       <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27135-2026 karta.png", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 18378-2026 karta.png", "A 18378-2026")</f>
         <v/>
       </c>
       <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27135-2026 georefererad karta.tif", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 18378-2026 georefererad karta.tif", "A 18378-2026")</f>
         <v/>
       </c>
       <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27135-2026 FSC-klagomål.docx", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 18378-2026 FSC-klagomål.docx", "A 18378-2026")</f>
         <v/>
       </c>
       <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27135-2026 FSC-klagomål mail.docx", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 18378-2026 FSC-klagomål mail.docx", "A 18378-2026")</f>
         <v/>
       </c>
       <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27135-2026 tillsynsbegäran.docx", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 18378-2026 tillsynsbegäran.docx", "A 18378-2026")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27135-2026 tillsynsbegäran mail.docx", "A 27135-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 18378-2026 tillsynsbegäran mail.docx", "A 18378-2026")</f>
         <v/>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 5233-2026</t>
+          <t>A 52261-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46049</v>
+        <v>44873</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,120 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>9</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Vedskivlav
+Hasselticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 5233-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>6</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Spillkråka
@@ -1709,144 +1817,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 52261-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44873</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Vedskivlav
-Hasselticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8939-2023</t>
+          <t>A 1561-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44979</v>
+        <v>44937</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,13 +2534,13 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -2567,796 +2567,796 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka
+Blåsippa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 10059-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>17</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bolmört
+Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Gullpudra
 Strutbräken</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="D23" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 12033-2026</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>2.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J26" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Fjällvråk
 Havsörn</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 1561-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44937</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>5</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka
-Blåsippa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 10059-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Bolmört
-Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44917</v>
+        <v>45119</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3385,8 +3385,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>15.8</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3422,46 +3427,50 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3475,10 +3484,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45279</v>
+        <v>44917</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3491,7 +3500,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>15.8</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3524,49 +3533,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3580,10 +3589,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45118</v>
+        <v>45119</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3601,31 +3610,31 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>13.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3634,49 +3643,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3686,14 +3695,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45119</v>
+        <v>44979</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3711,10 +3720,10 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>12.4</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -3723,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3735,10 +3744,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3751,42 +3760,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3800,10 +3809,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45558</v>
+        <v>45098</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3816,10 +3825,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -3856,42 +3865,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3905,10 +3914,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45119</v>
+        <v>45118</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3926,13 +3935,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3959,53 +3968,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4019,10 +4024,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46167</v>
+        <v>44965</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4034,37 +4039,32 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>7.9</v>
+        <v>1.8</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4076,46 +4076,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45098</v>
+        <v>45558</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -4185,42 +4185,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,8 +4249,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>12.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4259,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4274,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4290,42 +4295,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4335,14 +4340,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44979</v>
+        <v>45279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4354,13 +4359,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4384,58 +4384,58 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45119</v>
+        <v>46167</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4470,16 +4470,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13.1</v>
+        <v>7.9</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4506,39 +4506,39 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44809</v>
+        <v>45610</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45419</v>
+        <v>45274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45469</v>
+        <v>44986</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44979</v>
+        <v>44509</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5236,8 +5236,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5280,7 +5285,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5294,10 +5299,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44957</v>
+        <v>44680</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5310,7 +5315,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5353,7 +5358,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5367,10 +5372,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44979</v>
+        <v>44789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5383,7 +5388,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5426,7 +5431,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5440,10 +5445,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44574</v>
+        <v>44957</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5455,13 +5460,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5504,7 +5504,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44979</v>
+        <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5533,13 +5533,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>8.1</v>
+        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5582,7 +5577,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5596,10 +5591,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44602</v>
+        <v>45266</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5612,7 +5607,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5655,7 +5650,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5669,10 +5664,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45825</v>
+        <v>45520</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5684,13 +5679,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5733,7 +5723,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5747,10 +5737,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45928</v>
+        <v>45196</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5763,7 +5753,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5806,7 +5796,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5820,10 +5810,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45610</v>
+        <v>45189</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5836,7 +5826,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5879,7 +5869,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5893,10 +5883,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45737</v>
+        <v>45664</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5909,7 +5899,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5952,7 +5942,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5966,10 +5956,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45935</v>
+        <v>45747</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5982,7 +5972,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6025,7 +6015,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6039,10 +6029,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45400</v>
+        <v>45239</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,8 +6044,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6098,7 +6093,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6112,10 +6107,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45869</v>
+        <v>45457</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6128,7 +6123,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6171,7 +6166,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6185,10 +6180,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45869</v>
+        <v>45469</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6201,7 +6196,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6258,10 +6253,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46052</v>
+        <v>45610</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6273,13 +6268,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6322,7 +6312,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 52859-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6332,14 +6322,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45952</v>
+        <v>45610</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6352,7 +6342,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6395,7 +6385,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6409,10 +6399,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45610</v>
+        <v>44735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6425,7 +6415,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6468,7 +6458,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6482,10 +6472,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45086</v>
+        <v>45149</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6498,7 +6488,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6541,7 +6531,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6555,10 +6545,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45139</v>
+        <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6571,7 +6561,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6614,7 +6604,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 52859-2024</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6628,10 +6618,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45610</v>
+        <v>45139</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6644,7 +6634,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6687,7 +6677,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6701,10 +6691,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44509</v>
+        <v>45146</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6716,13 +6706,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6765,7 +6750,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6779,10 +6764,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45974</v>
+        <v>45140</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6795,7 +6780,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6838,7 +6823,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6848,14 +6833,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45974</v>
+        <v>45344</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6868,7 +6853,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6911,7 +6896,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6925,10 +6910,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45457</v>
+        <v>44574</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6940,8 +6925,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6984,7 +6974,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6998,10 +6988,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45610</v>
+        <v>45779</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7014,7 +7004,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7057,7 +7047,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7071,10 +7061,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45196</v>
+        <v>45184</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7087,7 +7077,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7130,7 +7120,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45113</v>
+        <v>44602</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7160,7 +7150,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7203,7 +7193,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7217,10 +7207,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45762</v>
+        <v>45789</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7232,8 +7222,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7276,7 +7271,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7290,10 +7285,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45140</v>
+        <v>45419</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7306,7 +7301,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7349,7 +7344,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7359,14 +7354,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44908</v>
+        <v>45113</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7379,7 +7374,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7422,7 +7417,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7436,10 +7431,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44979</v>
+        <v>45280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7451,13 +7446,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7500,7 +7490,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7514,10 +7504,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45196</v>
+        <v>44942</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7530,7 +7520,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7573,7 +7563,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7583,14 +7573,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44942</v>
+        <v>45561</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7603,7 +7593,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7646,7 +7636,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7660,10 +7650,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45469</v>
+        <v>44809</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7676,7 +7666,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7719,7 +7709,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7733,10 +7723,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45419</v>
+        <v>45173</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7749,7 +7739,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>6.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7792,7 +7782,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7806,10 +7796,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45062</v>
+        <v>45173</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7822,7 +7812,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.8</v>
+        <v>12.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7865,7 +7855,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7879,10 +7869,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45149</v>
+        <v>45280</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7895,7 +7885,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7938,7 +7928,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 48978-2023</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7952,10 +7942,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45209</v>
+        <v>45196</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7967,13 +7957,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8016,7 +8001,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 48978-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8030,10 +8015,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45173</v>
+        <v>45209</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8045,8 +8030,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8089,7 +8079,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8103,10 +8093,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44735</v>
+        <v>45825</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8118,8 +8108,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8162,7 +8157,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8176,10 +8171,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45274</v>
+        <v>45419</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8192,7 +8187,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8235,7 +8230,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8249,10 +8244,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46170</v>
+        <v>45469</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8265,7 +8260,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8308,7 +8303,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8322,10 +8317,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45280</v>
+        <v>44979</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8337,8 +8332,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.7</v>
+        <v>8.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8381,7 +8381,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8395,10 +8395,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45239</v>
+        <v>45028</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8410,13 +8410,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8459,7 +8454,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8473,10 +8468,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45266</v>
+        <v>45610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8489,7 +8484,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8532,7 +8527,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8542,14 +8537,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45344</v>
+        <v>45737</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8605,7 +8600,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8619,10 +8614,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45173</v>
+        <v>44979</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8635,7 +8630,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8678,7 +8673,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8692,10 +8687,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45272</v>
+        <v>44941</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8751,7 +8746,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8761,14 +8756,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46085</v>
+        <v>45062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8781,7 +8776,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8824,7 +8819,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8838,10 +8833,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46210</v>
+        <v>44979</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8853,8 +8848,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44680</v>
+        <v>44979</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45189</v>
+        <v>45869</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>7.6</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9043,7 +9043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45280</v>
+        <v>45869</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>5.6</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9116,7 +9116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45610</v>
+        <v>45086</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45184</v>
+        <v>44574</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9218,8 +9218,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9262,7 +9267,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9276,10 +9281,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45520</v>
+        <v>45935</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9292,7 +9297,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9335,7 +9340,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9349,10 +9354,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45146</v>
+        <v>45610</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9365,7 +9370,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9408,7 +9413,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9418,14 +9423,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44789</v>
+        <v>45952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9438,7 +9443,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9481,7 +9486,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9495,10 +9500,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46237</v>
+        <v>45928</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9516,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9554,7 +9559,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9568,10 +9573,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46237</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9584,7 +9589,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9627,7 +9632,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9641,10 +9646,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45028</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9657,7 +9662,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>6.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9700,7 +9705,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9714,10 +9719,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44986</v>
+        <v>46052</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9729,8 +9734,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9773,7 +9783,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9787,10 +9797,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45664</v>
+        <v>45762</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9813,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>11</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9846,7 +9856,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9856,14 +9866,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44941</v>
+        <v>44908</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9886,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9919,7 +9929,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9933,10 +9943,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46245</v>
+        <v>46170</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9959,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9992,7 +10002,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10006,10 +10016,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45561</v>
+        <v>46085</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10032,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10065,7 +10075,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10079,10 +10089,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45747</v>
+        <v>46210</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10105,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10138,7 +10148,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10152,10 +10162,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10178,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10211,7 +10221,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10225,10 +10235,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10251,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10284,7 +10294,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10298,10 +10308,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10324,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10357,7 +10367,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10371,10 +10381,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44574</v>
+        <v>46245</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10384,11 +10394,6 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -10435,7 +10440,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10449,10 +10454,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45779</v>
+        <v>46245</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10465,7 +10470,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10508,7 +10513,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10522,10 +10527,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45789</v>
+        <v>46245</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10537,13 +10542,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45846</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46188</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46125</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 52261-2022</t>
+          <t>A 5233-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44873</v>
+        <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1663,16 +1663,16 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1696,12 +1696,124 @@
         <v>4</v>
       </c>
       <c r="T11" t="n">
+        <v>6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Spillkråka
+Kråka
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 52261-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44873</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="T12" t="n">
         <v>9</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Vedskivlav
@@ -1709,144 +1821,32 @@
 Blåsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 52261-2022 artfynd.xlsx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 52261-2022 karta.png", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 52261-2022 georefererad karta.tif", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 52261-2022 FSC-klagomål.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 52261-2022 FSC-klagomål mail.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 52261-2022 tillsynsbegäran.docx", "A 52261-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 52261-2022 tillsynsbegäran mail.docx", "A 52261-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 5233-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46049</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Spillkråka
-Kråka
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 5233-2026 artfynd.xlsx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 5233-2026 karta.png", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 5233-2026 georefererad karta.tif", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 5233-2026 FSC-klagomål.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 5233-2026 FSC-klagomål mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 5233-2026 tillsynsbegäran.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 5233-2026 tillsynsbegäran mail.docx", "A 5233-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 5233-2026 prioriterade fågelarter.docx", "A 5233-2026")</f>
         <v/>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>45266</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44670</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>45789</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>44960</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1561-2023</t>
+          <t>A 12033-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2514,14 +2514,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44937</v>
+        <v>46085</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2534,16 +2534,16 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2567,796 +2567,796 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Fjällvråk
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 8939-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44979</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 47093-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45196</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hasselticka
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 1561-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U22" t="n">
         <v>5</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Blåsippa</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 1561-2023 artfynd.xlsx", "A 1561-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 1561-2023 karta.png", "A 1561-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 1561-2023 georefererad karta.tif", "A 1561-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 1561-2023 FSC-klagomål.docx", "A 1561-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 1561-2023 FSC-klagomål mail.docx", "A 1561-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 1561-2023 tillsynsbegäran.docx", "A 1561-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 1561-2023 tillsynsbegäran mail.docx", "A 1561-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 64189-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45279</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Gullviva</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 33528-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45131</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Gullpudra
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 49523-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Grönpyrola
+Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 10059-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>44621</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>17</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Bolmört
 Bollvitmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 10059-2022 artfynd.xlsx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 10059-2022 karta.png", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 10059-2022 georefererad karta.tif", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 10059-2022 FSC-klagomål.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 10059-2022 FSC-klagomål mail.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 10059-2022 tillsynsbegäran.docx", "A 10059-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 10059-2022 tillsynsbegäran mail.docx", "A 10059-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 47093-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45196</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hasselticka
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 47093-2023 artfynd.xlsx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 47093-2023 karta.png", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 47093-2023 georefererad karta.tif", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 47093-2023 FSC-klagomål.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 47093-2023 FSC-klagomål mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 47093-2023 tillsynsbegäran.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 47093-2023 tillsynsbegäran mail.docx", "A 47093-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8939-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44979</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 8939-2023 artfynd.xlsx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 8939-2023 karta.png", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 8939-2023 georefererad karta.tif", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 8939-2023 FSC-klagomål.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 8939-2023 FSC-klagomål mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 8939-2023 tillsynsbegäran.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 8939-2023 tillsynsbegäran mail.docx", "A 8939-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 33528-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45131</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Gullpudra
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 33528-2023 artfynd.xlsx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 33528-2023 karta.png", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 33528-2023 georefererad karta.tif", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 33528-2023 FSC-klagomål.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 33528-2023 FSC-klagomål mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 33528-2023 tillsynsbegäran.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 33528-2023 tillsynsbegäran mail.docx", "A 33528-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 49523-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Grönpyrola
-Västlig hakmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 49523-2023 artfynd.xlsx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 49523-2023 karta.png", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 49523-2023 georefererad karta.tif", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 49523-2023 FSC-klagomål.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 49523-2023 FSC-klagomål mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 49523-2023 tillsynsbegäran.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 49523-2023 tillsynsbegäran mail.docx", "A 49523-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 64189-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45279</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Gullviva</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64189-2023 artfynd.xlsx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64189-2023 karta.png", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64189-2023 georefererad karta.tif", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64189-2023 FSC-klagomål.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64189-2023 FSC-klagomål mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64189-2023 tillsynsbegäran.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64189-2023 tillsynsbegäran mail.docx", "A 64189-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 12033-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NYNÄSHAMN</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Fjällvråk
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 12033-2026 artfynd.xlsx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 12033-2026 karta.png", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 12033-2026 georefererad karta.tif", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 12033-2026 FSC-klagomål.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 12033-2026 FSC-klagomål mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 12033-2026 tillsynsbegäran.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 12033-2026 tillsynsbegäran mail.docx", "A 12033-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 12033-2026 prioriterade fågelarter.docx", "A 12033-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32011-2023</t>
+          <t>A 62634-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45119</v>
+        <v>44917</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3385,13 +3385,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>15.8</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -3427,50 +3422,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62634-2022</t>
+          <t>A 64196-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3484,10 +3475,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44917</v>
+        <v>45279</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3500,7 +3491,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>15.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
@@ -3533,49 +3524,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 62634-2022 artfynd.xlsx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 62634-2022 karta.png", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 62634-2022 georefererad karta.tif", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 62634-2022 FSC-klagomål.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 62634-2022 FSC-klagomål mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 62634-2022 tillsynsbegäran.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 62634-2022 tillsynsbegäran mail.docx", "A 62634-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32074-2023</t>
+          <t>A 31842-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3589,10 +3580,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45119</v>
+        <v>45118</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3610,16 +3601,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>13.1</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3634,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3643,49 +3634,49 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Grå kantarell</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 9017-2023</t>
+          <t>A 23906-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3695,14 +3686,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44979</v>
+        <v>46167</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3720,19 +3711,19 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3744,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3756,46 +3747,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 27748-2023</t>
+          <t>A 32092-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3809,10 +3800,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45098</v>
+        <v>45119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3824,14 +3815,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3865,42 +3861,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skärmstarr</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 31842-2023</t>
+          <t>A 40895-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3914,10 +3910,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45118</v>
+        <v>45558</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3929,16 +3925,11 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -3968,49 +3959,49 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 31842-2023 artfynd.xlsx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 31842-2023 karta.png", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 31842-2023 georefererad karta.tif", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 31842-2023 FSC-klagomål.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 31842-2023 FSC-klagomål mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 31842-2023 tillsynsbegäran.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 31842-2023 tillsynsbegäran mail.docx", "A 31842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6435-2023</t>
+          <t>A 32011-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4024,10 +4015,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44965</v>
+        <v>45119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4039,17 +4030,22 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.8</v>
+        <v>5.4</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -4064,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4080,42 +4076,46 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32011-2023 artfynd.xlsx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32011-2023 karta.png", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32011-2023 georefererad karta.tif", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32011-2023 FSC-klagomål.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32011-2023 FSC-klagomål mail.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32011-2023 tillsynsbegäran.docx", "A 32011-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32011-2023 tillsynsbegäran mail.docx", "A 32011-2023")</f>
+        <v/>
+      </c>
+      <c r="AE33">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/fåglar/A 32011-2023 prioriterade fågelarter.docx", "A 32011-2023")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 40895-2024</t>
+          <t>A 27748-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45558</v>
+        <v>45098</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>1</v>
@@ -4185,42 +4185,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 40895-2024 artfynd.xlsx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 27748-2023 artfynd.xlsx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 40895-2024 karta.png", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 27748-2023 karta.png", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 40895-2024 georefererad karta.tif", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 27748-2023 georefererad karta.tif", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 40895-2024 FSC-klagomål.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 27748-2023 FSC-klagomål.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 40895-2024 FSC-klagomål mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 27748-2023 FSC-klagomål mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 40895-2024 tillsynsbegäran.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 27748-2023 tillsynsbegäran.docx", "A 27748-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 40895-2024 tillsynsbegäran mail.docx", "A 40895-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 27748-2023 tillsynsbegäran mail.docx", "A 27748-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32092-2023</t>
+          <t>A 6435-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4234,10 +4234,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45119</v>
+        <v>44965</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4249,13 +4249,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>12.4</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4264,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4279,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4295,42 +4290,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32092-2023 artfynd.xlsx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 6435-2023 artfynd.xlsx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32092-2023 karta.png", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 6435-2023 karta.png", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32092-2023 georefererad karta.tif", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 6435-2023 georefererad karta.tif", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32092-2023 FSC-klagomål.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 6435-2023 FSC-klagomål.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32092-2023 FSC-klagomål mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 6435-2023 FSC-klagomål mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32092-2023 tillsynsbegäran.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 6435-2023 tillsynsbegäran.docx", "A 6435-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32092-2023 tillsynsbegäran mail.docx", "A 32092-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 6435-2023 tillsynsbegäran mail.docx", "A 6435-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 64196-2023</t>
+          <t>A 9017-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4340,14 +4335,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45279</v>
+        <v>44979</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,8 +4354,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4384,58 +4384,58 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 64196-2023 artfynd.xlsx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 9017-2023 artfynd.xlsx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 64196-2023 karta.png", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 9017-2023 karta.png", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 64196-2023 georefererad karta.tif", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 9017-2023 georefererad karta.tif", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 64196-2023 FSC-klagomål.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 9017-2023 FSC-klagomål.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 64196-2023 FSC-klagomål mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 9017-2023 FSC-klagomål mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 64196-2023 tillsynsbegäran.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 9017-2023 tillsynsbegäran.docx", "A 9017-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 64196-2023 tillsynsbegäran mail.docx", "A 64196-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 9017-2023 tillsynsbegäran mail.docx", "A 9017-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23906-2026</t>
+          <t>A 32074-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4449,10 +4449,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46167</v>
+        <v>45119</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4470,31 +4470,31 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.9</v>
+        <v>13.1</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4506,39 +4506,39 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grå kantarell</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 23906-2026 artfynd.xlsx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 32074-2023 artfynd.xlsx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 23906-2026 karta.png", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor/A 32074-2023 karta.png", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 23906-2026 georefererad karta.tif", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/kartor_geotiff/A 32074-2023 georefererad karta.tif", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 23906-2026 FSC-klagomål.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomål/A 32074-2023 FSC-klagomål.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 23906-2026 FSC-klagomål mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/klagomålsmail/A 32074-2023 FSC-klagomål mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 23906-2026 tillsynsbegäran.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsyn/A 32074-2023 tillsynsbegäran.docx", "A 32074-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 23906-2026 tillsynsbegäran mail.docx", "A 23906-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/tillsynsmail/A 32074-2023 tillsynsbegäran mail.docx", "A 32074-2023")</f>
         <v/>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
         <v>44621</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>44538</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>44553</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>44553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>44854</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 52911-2024</t>
+          <t>A 37491-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45610</v>
+        <v>44809</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63463-2023</t>
+          <t>A 17991-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45274</v>
+        <v>45419</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10224-2023</t>
+          <t>A 26501-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5148,10 +5148,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44986</v>
+        <v>45469</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 63931-2021</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44509</v>
+        <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5236,13 +5236,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5285,7 +5280,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17634-2022</t>
+          <t>A 8932-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5299,10 +5294,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44680</v>
+        <v>44979</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5315,7 +5310,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5358,7 +5353,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 33667-2022</t>
+          <t>A 4688-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5372,10 +5367,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44789</v>
+        <v>44957</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5388,7 +5383,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5431,7 +5426,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 4688-2023</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5445,10 +5440,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44957</v>
+        <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5460,8 +5455,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5504,7 +5504,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62878-2023</t>
+          <t>A 9020-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45272</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5533,8 +5533,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5577,7 +5582,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62038-2023</t>
+          <t>A 5884-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5591,10 +5596,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45266</v>
+        <v>46052</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5606,8 +5611,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5650,7 +5660,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 33787-2024</t>
+          <t>A 6775-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5664,10 +5674,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45520</v>
+        <v>44602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5680,7 +5690,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.2</v>
+        <v>4.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5723,7 +5733,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47128-2023</t>
+          <t>A 46857-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5737,10 +5747,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45196</v>
+        <v>45928</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5753,7 +5763,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5796,7 +5806,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 44619-2023</t>
+          <t>A 48456-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5810,10 +5820,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45189</v>
+        <v>45935</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5826,7 +5836,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5869,7 +5879,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 636-2025</t>
+          <t>A 51954-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5879,14 +5889,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45664</v>
+        <v>45952</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5942,7 +5952,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 15465-2025</t>
+          <t>A 15176-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5956,10 +5966,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45747</v>
+        <v>45400</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5972,7 +5982,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6015,7 +6025,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 55871-2023</t>
+          <t>A 56210-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6029,10 +6039,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45239</v>
+        <v>45974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6044,13 +6054,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6093,7 +6098,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 24288-2024</t>
+          <t>A 56385-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6107,10 +6112,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45457</v>
+        <v>45974</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6123,7 +6128,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.3</v>
+        <v>6.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6166,7 +6171,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 26505-2024</t>
+          <t>A 25175-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6180,10 +6185,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45469</v>
+        <v>45086</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6196,7 +6201,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6239,7 +6244,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 52910-2024</t>
+          <t>A 34385-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6253,10 +6258,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45610</v>
+        <v>45139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6269,7 +6274,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6329,7 +6334,7 @@
         <v>45610</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6385,7 +6390,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 26190-2022</t>
+          <t>A 63931-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6399,10 +6404,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44735</v>
+        <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6414,8 +6419,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6458,7 +6468,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 36052-2023</t>
+          <t>A 18411-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6472,10 +6482,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45149</v>
+        <v>45762</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6488,7 +6498,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.9</v>
+        <v>11</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6531,7 +6541,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15176-2024</t>
+          <t>A 24288-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6545,10 +6555,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45400</v>
+        <v>45457</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6561,7 +6571,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6604,7 +6614,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34385-2023</t>
+          <t>A 52911-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6618,10 +6628,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45139</v>
+        <v>45610</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6634,7 +6644,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6677,7 +6687,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 35356-2023</t>
+          <t>A 60977-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6687,14 +6697,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45146</v>
+        <v>44908</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6717,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6750,7 +6760,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 34660-2023</t>
+          <t>A 47089-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6764,10 +6774,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45140</v>
+        <v>45196</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6790,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6823,7 +6833,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7180-2024</t>
+          <t>A 29811-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6833,14 +6843,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45344</v>
+        <v>45825</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6852,8 +6862,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6896,7 +6911,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 52953-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6910,10 +6925,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44574</v>
+        <v>45610</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6925,13 +6940,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6974,7 +6984,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21202-2025</t>
+          <t>A 13945-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6988,10 +6998,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45779</v>
+        <v>45737</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7014,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7047,7 +7057,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44624-2023</t>
+          <t>A 30910-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7061,10 +7071,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45184</v>
+        <v>45113</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7087,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.8</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7120,7 +7130,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 6775-2022</t>
+          <t>A 36468-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44602</v>
+        <v>45869</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7160,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7193,7 +7203,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22730-2025</t>
+          <t>A 36496-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7207,10 +7217,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45789</v>
+        <v>45869</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7222,13 +7232,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7271,7 +7276,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17990-2024</t>
+          <t>A 52950-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7285,10 +7290,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45419</v>
+        <v>45610</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7301,7 +7306,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7344,7 +7349,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30910-2023</t>
+          <t>A 34660-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7358,10 +7363,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45113</v>
+        <v>45140</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7374,7 +7379,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7417,7 +7422,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 64411-2023</t>
+          <t>A 9062-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45280</v>
+        <v>44979</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7446,8 +7451,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7490,7 +7500,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 2367-2023</t>
+          <t>A 47128-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7504,10 +7514,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44942</v>
+        <v>45196</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7530,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7563,7 +7573,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41767-2024</t>
+          <t>A 2367-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7573,14 +7583,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45561</v>
+        <v>44942</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7603,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7636,7 +7646,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37491-2022</t>
+          <t>A 24595-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7650,10 +7660,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44809</v>
+        <v>46170</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7676,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7709,7 +7719,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41677-2023</t>
+          <t>A 26505-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7723,10 +7733,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45173</v>
+        <v>45469</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7739,7 +7749,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7782,7 +7792,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41680-2023</t>
+          <t>A 17990-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7796,10 +7806,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45173</v>
+        <v>45419</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7812,7 +7822,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>12.3</v>
+        <v>0.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7855,7 +7865,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 64494-2023</t>
+          <t>A 21192-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7869,10 +7879,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45280</v>
+        <v>45062</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7885,7 +7895,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7928,7 +7938,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47089-2023</t>
+          <t>A 36052-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7942,10 +7952,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45196</v>
+        <v>45149</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7958,7 +7968,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8018,7 +8028,7 @@
         <v>45209</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8079,7 +8089,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 29811-2025</t>
+          <t>A 41680-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8093,10 +8103,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45825</v>
+        <v>45173</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8108,13 +8118,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>4.7</v>
+        <v>12.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8162,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17991-2024</t>
+          <t>A 26190-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8171,10 +8176,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45419</v>
+        <v>44735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8187,7 +8192,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8230,7 +8235,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 26501-2024</t>
+          <t>A 12032-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8240,14 +8245,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45469</v>
+        <v>46085</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8265,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8308,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 9020-2023</t>
+          <t>A 63463-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8317,10 +8322,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44979</v>
+        <v>45274</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8332,13 +8337,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>8.1</v>
+        <v>0.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8381,7 +8381,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16793-2023</t>
+          <t>A 30476-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8395,10 +8395,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45028</v>
+        <v>46210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8454,7 +8454,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52953-2024</t>
+          <t>A 64494-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45610</v>
+        <v>45280</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8527,7 +8527,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13945-2025</t>
+          <t>A 55871-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45737</v>
+        <v>45239</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8556,8 +8556,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8600,7 +8605,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 62038-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8614,10 +8619,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44979</v>
+        <v>45266</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8630,7 +8635,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>5.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8673,7 +8678,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2170-2023</t>
+          <t>A 7180-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8683,14 +8688,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44941</v>
+        <v>45344</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8703,7 +8708,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8746,7 +8751,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21192-2023</t>
+          <t>A 41677-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8760,10 +8765,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45062</v>
+        <v>45173</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8776,7 +8781,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8819,7 +8824,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 9062-2023</t>
+          <t>A 62878-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8833,10 +8838,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44979</v>
+        <v>45272</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8848,13 +8853,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8932-2023</t>
+          <t>A 17634-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8911,10 +8911,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44979</v>
+        <v>44680</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8970,7 +8970,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 36496-2025</t>
+          <t>A 32305-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8984,10 +8984,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45869</v>
+        <v>46237</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9043,7 +9043,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 36468-2025</t>
+          <t>A 32307-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45869</v>
+        <v>46237</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9116,7 +9116,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 25175-2023</t>
+          <t>A 44619-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9130,10 +9130,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45086</v>
+        <v>45189</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>7.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9189,7 +9189,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1658-2022</t>
+          <t>A 64411-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44574</v>
+        <v>45280</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9218,13 +9218,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9267,7 +9262,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48456-2025</t>
+          <t>A 52910-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9281,10 +9276,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45935</v>
+        <v>45610</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9297,7 +9292,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9340,7 +9335,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52950-2024</t>
+          <t>A 33060-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9354,10 +9349,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45610</v>
+        <v>46245</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9370,7 +9365,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9413,7 +9408,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51954-2025</t>
+          <t>A 44624-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9423,14 +9418,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45952</v>
+        <v>45184</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9443,7 +9438,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>6.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9486,7 +9481,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 46857-2025</t>
+          <t>A 32840-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9500,10 +9495,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45928</v>
+        <v>46244</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9516,7 +9511,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9559,7 +9554,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56210-2025</t>
+          <t>A 33067-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9573,10 +9568,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>46245</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9589,7 +9584,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9632,7 +9627,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56385-2025</t>
+          <t>A 33063-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9646,10 +9641,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>46245</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9662,7 +9657,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>6.1</v>
+        <v>2.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9705,7 +9700,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 5884-2026</t>
+          <t>A 33787-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9719,10 +9714,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46052</v>
+        <v>45520</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9734,13 +9729,8 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9783,7 +9773,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18411-2025</t>
+          <t>A 35356-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9797,10 +9787,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45762</v>
+        <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9813,7 +9803,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>11</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9856,7 +9846,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 60977-2022</t>
+          <t>A 33667-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9866,14 +9856,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44908</v>
+        <v>44789</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9886,7 +9876,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9929,7 +9919,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 24595-2026</t>
+          <t>A 16793-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9943,10 +9933,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46170</v>
+        <v>45028</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9959,7 +9949,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10002,7 +9992,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12032-2026</t>
+          <t>A 10224-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10012,14 +10002,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46085</v>
+        <v>44986</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10032,7 +10022,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10075,7 +10065,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 30476-2026</t>
+          <t>A 636-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10089,10 +10079,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46210</v>
+        <v>45664</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10105,7 +10095,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10148,7 +10138,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32305-2026</t>
+          <t>A 2170-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10162,10 +10152,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46237</v>
+        <v>44941</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10178,7 +10168,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10221,7 +10211,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 32307-2026</t>
+          <t>A 41767-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10231,14 +10221,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46237</v>
+        <v>45561</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10251,7 +10241,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10294,7 +10284,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 32840-2026</t>
+          <t>A 15465-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10308,10 +10298,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46244</v>
+        <v>45747</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10314,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10367,7 +10357,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 33060-2026</t>
+          <t>A 1658-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10381,10 +10371,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46245</v>
+        <v>44574</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10394,6 +10384,11 @@
       <c r="G117" t="inlineStr">
         <is>
           <t>NYNÄSHAMN</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -10440,7 +10435,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 33067-2026</t>
+          <t>A 21202-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10454,10 +10449,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46245</v>
+        <v>45779</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10465,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10513,7 +10508,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 33063-2026</t>
+          <t>A 22730-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10527,10 +10522,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46245</v>
+        <v>45789</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10542,8 +10537,13 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
         <v>45482</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         <v>44787</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>46198</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>

--- a/Översikt NYNÄSHAMN.xlsx
+++ b/Översikt NYNÄSHAMN.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE122"/>
+  <dimension ref="A1:AE121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>44935</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45113</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>45257</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>45482</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>45846</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>46188</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>46125</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>46245</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
         <v>46049</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>44873</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>46198</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>44980</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 62013-2023</t>
+          <t>A 22716-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45266</v>
+        <v>45789</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2097,14 +2097,19 @@
           <t>NYNÄSHAMN</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -2131,274 +2136,269 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Björksplintborre
+Stekelbock
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0192/artfynd/A 22716-2025 artfynd.xlsx", "A 22716-2025")</f>
+        <v/>